--- a/data/vessels/2026-10-12.xlsx
+++ b/data/vessels/2026-10-12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://portoftacoma.sharepoint.com/sites/dnateam-Technical/Shared Documents/Technical/External Dashboards/Vessel Schedule/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="418509" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A605C0A4-9698-44D4-AB62-D598A2262D4E}"/>
+  <xr:revisionPtr revIDLastSave="419729" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0A76BFF8-5344-4CF6-8E0D-4EC2E0AC78D7}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6E7AA7D4-05A2-4831-A105-C5B1AC660A61}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="948" uniqueCount="228">
   <si>
     <t>Harbor</t>
   </si>
@@ -146,25 +146,256 @@
     <t>UK638R</t>
   </si>
   <si>
+    <t>WUT</t>
+  </si>
+  <si>
+    <t>PN1</t>
+  </si>
+  <si>
+    <t>ONE MAESTRO</t>
+  </si>
+  <si>
+    <t>088W</t>
+  </si>
+  <si>
+    <t>MSC BOSTON</t>
+  </si>
+  <si>
+    <t>MC641R</t>
+  </si>
+  <si>
+    <t>MSC PINA</t>
+  </si>
+  <si>
+    <t>UK639R</t>
+  </si>
+  <si>
     <t>In transit</t>
   </si>
   <si>
-    <t>WUT</t>
-  </si>
-  <si>
-    <t>PN1</t>
-  </si>
-  <si>
-    <t>ONE MAESTRO</t>
-  </si>
-  <si>
-    <t>088W</t>
+    <t>WST</t>
+  </si>
+  <si>
+    <t>Matson - AK</t>
+  </si>
+  <si>
+    <t>R.J. PFEIFFER</t>
+  </si>
+  <si>
+    <t>641S</t>
+  </si>
+  <si>
+    <t>Matson</t>
+  </si>
+  <si>
+    <t>SSA Marine</t>
+  </si>
+  <si>
+    <t>PN3</t>
+  </si>
+  <si>
+    <t>HYUNDAI SUPREME</t>
+  </si>
+  <si>
+    <t>PN32635W</t>
+  </si>
+  <si>
+    <t>HMM</t>
+  </si>
+  <si>
+    <t>Waiting 1.1 days</t>
+  </si>
+  <si>
+    <t>EB1</t>
+  </si>
+  <si>
+    <t>RCC TIANJIN</t>
+  </si>
+  <si>
+    <t>018A</t>
+  </si>
+  <si>
+    <t>Hyundai Glovis</t>
+  </si>
+  <si>
+    <t>BERGAMOT ACE</t>
+  </si>
+  <si>
+    <t>158A</t>
   </si>
   <si>
     <t>T18</t>
   </si>
   <si>
-    <t>SM SEOUL</t>
+    <t>CMA CGM BYBLOS</t>
+  </si>
+  <si>
+    <t>CPN00/CPN01</t>
+  </si>
+  <si>
+    <t>CMA CGM</t>
+  </si>
+  <si>
+    <t>TOTE</t>
+  </si>
+  <si>
+    <t>Tote - AK1</t>
+  </si>
+  <si>
+    <t>MIDNIGHT SUN</t>
+  </si>
+  <si>
+    <t>Tote</t>
+  </si>
+  <si>
+    <t>Tote Maritime Alaska Inc</t>
+  </si>
+  <si>
+    <t>Multipurpose</t>
+  </si>
+  <si>
+    <t>Blair</t>
+  </si>
+  <si>
+    <t>LIBERTY PRIDE</t>
+  </si>
+  <si>
+    <t>Liberty</t>
+  </si>
+  <si>
+    <t>Pacific Terminals</t>
+  </si>
+  <si>
+    <t>Oceania</t>
+  </si>
+  <si>
+    <t>LONG BEACH EXPRESS</t>
+  </si>
+  <si>
+    <t>636N/642S</t>
+  </si>
+  <si>
+    <t>Hapag-Lloyd</t>
+  </si>
+  <si>
+    <t>EB Service 2</t>
+  </si>
+  <si>
+    <t>SUVA CHIEF</t>
+  </si>
+  <si>
+    <t>007E/008W</t>
+  </si>
+  <si>
+    <t>Swire</t>
+  </si>
+  <si>
+    <t>Talon Marine Services LLC</t>
+  </si>
+  <si>
+    <t>CLX</t>
+  </si>
+  <si>
+    <t>CAPE TAINARO</t>
+  </si>
+  <si>
+    <t>MC642R</t>
+  </si>
+  <si>
+    <t>MATSON KODIAK</t>
+  </si>
+  <si>
+    <t>PNW1</t>
+  </si>
+  <si>
+    <t>OOCL NEW YORK</t>
+  </si>
+  <si>
+    <t>122E/122W</t>
+  </si>
+  <si>
+    <t>OOCL</t>
+  </si>
+  <si>
+    <t>Matson - HI2</t>
+  </si>
+  <si>
+    <t>MANULANI</t>
+  </si>
+  <si>
+    <t>IRIS ACE</t>
+  </si>
+  <si>
+    <t>110A</t>
+  </si>
+  <si>
+    <t>Ro-Ro</t>
+  </si>
+  <si>
+    <t>Tote - AK2</t>
+  </si>
+  <si>
+    <t>NORTH STAR</t>
+  </si>
+  <si>
+    <t>WC4/TP5</t>
+  </si>
+  <si>
+    <t>MAERSK TORINO</t>
+  </si>
+  <si>
+    <t>639E/642W</t>
+  </si>
+  <si>
+    <t>Maersk</t>
+  </si>
+  <si>
+    <t>CPNW</t>
+  </si>
+  <si>
+    <t>CMA CGM ALMAVIVA</t>
+  </si>
+  <si>
+    <t>CPN02/CPN03</t>
+  </si>
+  <si>
+    <t>CPV</t>
+  </si>
+  <si>
+    <t>XIN YING KOU</t>
+  </si>
+  <si>
+    <t>269N/269S</t>
+  </si>
+  <si>
+    <t>COSCO</t>
+  </si>
+  <si>
+    <t>COSCO SHIPPING LINES</t>
+  </si>
+  <si>
+    <t>SALVIA ACE</t>
+  </si>
+  <si>
+    <t>177A</t>
+  </si>
+  <si>
+    <t>MODERN LINK</t>
+  </si>
+  <si>
+    <t>THEMISA</t>
+  </si>
+  <si>
+    <t>ED615</t>
+  </si>
+  <si>
+    <t>Wallenius</t>
+  </si>
+  <si>
+    <t>ONE OWL</t>
+  </si>
+  <si>
+    <t>SM QINGDAO</t>
   </si>
   <si>
     <t>2607E/2607W</t>
@@ -173,237 +404,6 @@
     <t>SM Line</t>
   </si>
   <si>
-    <t>MSC PINA</t>
-  </si>
-  <si>
-    <t>UK639R</t>
-  </si>
-  <si>
-    <t>CLX</t>
-  </si>
-  <si>
-    <t>MSC BOSTON</t>
-  </si>
-  <si>
-    <t>MC641R</t>
-  </si>
-  <si>
-    <t>WST</t>
-  </si>
-  <si>
-    <t>Matson - AK</t>
-  </si>
-  <si>
-    <t>R.J. PFEIFFER</t>
-  </si>
-  <si>
-    <t>641S</t>
-  </si>
-  <si>
-    <t>Matson</t>
-  </si>
-  <si>
-    <t>SSA Marine</t>
-  </si>
-  <si>
-    <t>PN3</t>
-  </si>
-  <si>
-    <t>HYUNDAI SUPREME</t>
-  </si>
-  <si>
-    <t>PN32635E</t>
-  </si>
-  <si>
-    <t>HMM</t>
-  </si>
-  <si>
-    <t>EB1</t>
-  </si>
-  <si>
-    <t>RCC TIANJIN</t>
-  </si>
-  <si>
-    <t>018A</t>
-  </si>
-  <si>
-    <t>Hyundai Glovis</t>
-  </si>
-  <si>
-    <t>BERGAMOT ACE</t>
-  </si>
-  <si>
-    <t>158A</t>
-  </si>
-  <si>
-    <t>CPNW</t>
-  </si>
-  <si>
-    <t>CMA CGM BYBLOS</t>
-  </si>
-  <si>
-    <t>CPN00/CPN01</t>
-  </si>
-  <si>
-    <t>CMA CGM</t>
-  </si>
-  <si>
-    <t>TOTE</t>
-  </si>
-  <si>
-    <t>Tote - AK1</t>
-  </si>
-  <si>
-    <t>MIDNIGHT SUN</t>
-  </si>
-  <si>
-    <t>Tote</t>
-  </si>
-  <si>
-    <t>Tote Maritime Alaska Inc</t>
-  </si>
-  <si>
-    <t>Multipurpose</t>
-  </si>
-  <si>
-    <t>Blair</t>
-  </si>
-  <si>
-    <t>LIBERTY PRIDE</t>
-  </si>
-  <si>
-    <t>Liberty</t>
-  </si>
-  <si>
-    <t>Pacific Terminals</t>
-  </si>
-  <si>
-    <t>Oceania</t>
-  </si>
-  <si>
-    <t>LONG BEACH EXPRESS</t>
-  </si>
-  <si>
-    <t>636N/642S</t>
-  </si>
-  <si>
-    <t>Hapag-Lloyd</t>
-  </si>
-  <si>
-    <t>EB Service 2</t>
-  </si>
-  <si>
-    <t>SUVA CHIEF</t>
-  </si>
-  <si>
-    <t>007E/008W</t>
-  </si>
-  <si>
-    <t>Swire</t>
-  </si>
-  <si>
-    <t>Talon Marine Services LLC</t>
-  </si>
-  <si>
-    <t>CAPE TAINARO</t>
-  </si>
-  <si>
-    <t>MC642R</t>
-  </si>
-  <si>
-    <t>MATSON KODIAK</t>
-  </si>
-  <si>
-    <t>PNW1</t>
-  </si>
-  <si>
-    <t>OOCL NEW YORK</t>
-  </si>
-  <si>
-    <t>122E/122W</t>
-  </si>
-  <si>
-    <t>OOCL</t>
-  </si>
-  <si>
-    <t>Matson - HI2</t>
-  </si>
-  <si>
-    <t>MANULANI</t>
-  </si>
-  <si>
-    <t>IRIS ACE</t>
-  </si>
-  <si>
-    <t>110A</t>
-  </si>
-  <si>
-    <t>Ro-Ro</t>
-  </si>
-  <si>
-    <t>Tote - AK2</t>
-  </si>
-  <si>
-    <t>NORTH STAR</t>
-  </si>
-  <si>
-    <t>WC4/TP5</t>
-  </si>
-  <si>
-    <t>MAERSK TORINO</t>
-  </si>
-  <si>
-    <t>639E/642W</t>
-  </si>
-  <si>
-    <t>Maersk</t>
-  </si>
-  <si>
-    <t>CMA CGM ALMAVIVA</t>
-  </si>
-  <si>
-    <t>CPN02/CPN03</t>
-  </si>
-  <si>
-    <t>CPV</t>
-  </si>
-  <si>
-    <t>XIN YING KOU</t>
-  </si>
-  <si>
-    <t>269N/269S</t>
-  </si>
-  <si>
-    <t>COSCO</t>
-  </si>
-  <si>
-    <t>COSCO SHIPPING LINES</t>
-  </si>
-  <si>
-    <t>THEMISA</t>
-  </si>
-  <si>
-    <t>ED615</t>
-  </si>
-  <si>
-    <t>Wallenius</t>
-  </si>
-  <si>
-    <t>MODERN LINK</t>
-  </si>
-  <si>
-    <t>SALVIA ACE</t>
-  </si>
-  <si>
-    <t>177A</t>
-  </si>
-  <si>
-    <t>SM QINGDAO</t>
-  </si>
-  <si>
-    <t>ONE OWL</t>
-  </si>
-  <si>
     <t>PCT</t>
   </si>
   <si>
@@ -425,7 +425,7 @@
     <t>YM COSMOS</t>
   </si>
   <si>
-    <t>YCOT0192E</t>
+    <t>JCOM0192E</t>
   </si>
   <si>
     <t>MSC DENISSE X</t>
@@ -521,28 +521,34 @@
     <t>RJ PFEIFFER</t>
   </si>
   <si>
+    <t>ARC INDEPENDENCE</t>
+  </si>
+  <si>
+    <t>ARC</t>
+  </si>
+  <si>
     <t>ARC HONOR</t>
   </si>
   <si>
     <t>ED616</t>
   </si>
   <si>
-    <t>ARC INDEPENDENCE</t>
-  </si>
-  <si>
-    <t>ARC</t>
-  </si>
-  <si>
     <t>EVER SALUTE</t>
   </si>
   <si>
-    <t>494129E</t>
+    <t>494-129E</t>
   </si>
   <si>
     <t>CMA CGM FORT JAMES</t>
   </si>
   <si>
-    <t>CPN0I0S</t>
+    <t>CPN040S19</t>
+  </si>
+  <si>
+    <t>YM WEALTH</t>
+  </si>
+  <si>
+    <t>JYMW0194E</t>
   </si>
   <si>
     <t>MSC IVANA</t>
@@ -551,16 +557,10 @@
     <t>UK638A</t>
   </si>
   <si>
-    <t>YM WEALTH</t>
-  </si>
-  <si>
-    <t>YMWT0193E</t>
-  </si>
-  <si>
     <t>YM PLUM</t>
   </si>
   <si>
-    <t>197E</t>
+    <t>JYPL0197E</t>
   </si>
   <si>
     <t>YM TUTORIAL</t>
@@ -572,102 +572,99 @@
     <t>SM PORTLAND</t>
   </si>
   <si>
+    <t>PATARA</t>
+  </si>
+  <si>
+    <t>005A</t>
+  </si>
+  <si>
+    <t>FRANKFURT EXPRESS</t>
+  </si>
+  <si>
+    <t>640E</t>
+  </si>
+  <si>
+    <t>Not Specified</t>
+  </si>
+  <si>
+    <t>ONE SYNERGY</t>
+  </si>
+  <si>
+    <t>JOYN0002E</t>
+  </si>
+  <si>
+    <t>ONE DURBAN</t>
+  </si>
+  <si>
+    <t>PN32639W</t>
+  </si>
+  <si>
+    <t>EVER MODE</t>
+  </si>
+  <si>
+    <t>1473-010E</t>
+  </si>
+  <si>
+    <t>MSC NITYA B</t>
+  </si>
+  <si>
+    <t>MC637A</t>
+  </si>
+  <si>
+    <t>NADI CHIEF</t>
+  </si>
+  <si>
+    <t>14E</t>
+  </si>
+  <si>
+    <t>SWIFT ACE</t>
+  </si>
+  <si>
+    <t>152A</t>
+  </si>
+  <si>
+    <t>MSC SOLA</t>
+  </si>
+  <si>
+    <t>UK639A</t>
+  </si>
+  <si>
+    <t>LAVENDER ACE</t>
+  </si>
+  <si>
+    <t>123A</t>
+  </si>
+  <si>
+    <t>HYUNDAI FORWARD</t>
+  </si>
+  <si>
+    <t>HHFW0172E</t>
+  </si>
+  <si>
+    <t>CYPRESS</t>
+  </si>
+  <si>
+    <t>MORNING LUCY</t>
+  </si>
+  <si>
+    <t>KW665</t>
+  </si>
+  <si>
+    <t>SM TIANJIN</t>
+  </si>
+  <si>
+    <t>ONE MAJESTY</t>
+  </si>
+  <si>
+    <t>JMJT0026E</t>
+  </si>
+  <si>
     <t>EVER SMILE</t>
   </si>
   <si>
     <t>495-136E</t>
   </si>
   <si>
-    <t>PATARA</t>
-  </si>
-  <si>
-    <t>005A</t>
-  </si>
-  <si>
-    <t>FRANKFURT EXPRESS</t>
-  </si>
-  <si>
-    <t>640E</t>
-  </si>
-  <si>
-    <t>Not Specified</t>
-  </si>
-  <si>
-    <t>ONE SYNERGY</t>
-  </si>
-  <si>
-    <t>2E</t>
-  </si>
-  <si>
-    <t>ONE DURBAN</t>
-  </si>
-  <si>
-    <t>NBBT0001E</t>
-  </si>
-  <si>
-    <t>EVER MODE</t>
-  </si>
-  <si>
-    <t>1473-010E</t>
-  </si>
-  <si>
-    <t>MSC NITYA B</t>
-  </si>
-  <si>
-    <t>MC637A</t>
-  </si>
-  <si>
-    <t>NADI CHIEF</t>
-  </si>
-  <si>
-    <t>14E</t>
-  </si>
-  <si>
-    <t>SWIFT ACE</t>
-  </si>
-  <si>
-    <t>152A</t>
-  </si>
-  <si>
-    <t>MSC SOLA</t>
-  </si>
-  <si>
-    <t>UK639A</t>
-  </si>
-  <si>
-    <t>LAVENDER ACE</t>
-  </si>
-  <si>
-    <t>123A</t>
-  </si>
-  <si>
-    <t>HYUNDAI FORWARD</t>
-  </si>
-  <si>
-    <t>172E</t>
-  </si>
-  <si>
-    <t>CYPRESS</t>
-  </si>
-  <si>
-    <t>CPN060S19</t>
-  </si>
-  <si>
-    <t>MORNING LUCY</t>
-  </si>
-  <si>
-    <t>KW665</t>
-  </si>
-  <si>
-    <t>SM TIANJIN</t>
-  </si>
-  <si>
-    <t>ONE MAJESTY</t>
-  </si>
-  <si>
-    <t>OMJT0026E</t>
-  </si>
-  <si>
     <t>SANTA RITA</t>
   </si>
   <si>
@@ -677,12 +674,6 @@
     <t>SM MUMBAI</t>
   </si>
   <si>
-    <t>EVER STRONG</t>
-  </si>
-  <si>
-    <t>497-134E</t>
-  </si>
-  <si>
     <t>BUDAPEST EXPRESS</t>
   </si>
   <si>
@@ -707,7 +698,7 @@
     <t>CORNEILLE</t>
   </si>
   <si>
-    <t>OILT0014E</t>
+    <t>JCLL0014E</t>
   </si>
   <si>
     <t>WESTWOOD COLUMBIA</t>
@@ -731,7 +722,7 @@
     <t>ONE FANTASTIC</t>
   </si>
   <si>
-    <t>FANT0011E</t>
+    <t>JOFN0011E</t>
   </si>
 </sst>
 </file>
@@ -804,10 +795,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}" name="Table1" displayName="Table1" ref="A1:L114" totalsRowShown="0">
-  <autoFilter ref="A1:L114" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L114">
-    <sortCondition ref="J2:J114"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}" name="Table1" displayName="Table1" ref="A1:L112" totalsRowShown="0">
+  <autoFilter ref="A1:L112" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L112">
+    <sortCondition ref="J2:J112"/>
   </sortState>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{3ED8A004-BAC7-4959-9663-633E38656002}" name="Harbor"/>
@@ -1144,7 +1135,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9E2A47A-528B-46DE-AE1C-82EC550E6AFE}">
-  <dimension ref="A1:L114"/>
+  <dimension ref="A1:L112"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="10.7109375" customWidth="1"/>
@@ -1403,7 +1394,7 @@
         <v>46308.166666666664</v>
       </c>
       <c r="L7" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -1411,16 +1402,16 @@
         <v>12</v>
       </c>
       <c r="B8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" t="s">
         <v>36</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>37</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="F8" t="s">
         <v>23</v>
@@ -1438,7 +1429,7 @@
         <v>46308.75</v>
       </c>
       <c r="L8" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -1446,16 +1437,19 @@
         <v>27</v>
       </c>
       <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" t="s">
+        <v>39</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D9" t="s">
-        <v>41</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="F9" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="G9" t="s">
         <v>17</v>
@@ -1464,13 +1458,13 @@
         <v>18</v>
       </c>
       <c r="J9" s="2">
-        <v>46307.25</v>
+        <v>46308.291666666664</v>
       </c>
       <c r="K9" s="2">
-        <v>46307.75</v>
+        <v>46309.75</v>
       </c>
       <c r="L9" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -1484,10 +1478,10 @@
         <v>32</v>
       </c>
       <c r="D10" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F10" t="s">
         <v>31</v>
@@ -1505,42 +1499,45 @@
         <v>46310.166666666664</v>
       </c>
       <c r="L10" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="C11" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" t="s">
         <v>46</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="F11" t="s">
         <v>48</v>
       </c>
-      <c r="F11" t="s">
-        <v>31</v>
-      </c>
       <c r="G11" t="s">
-        <v>17</v>
+        <v>48</v>
+      </c>
+      <c r="H11" t="s">
+        <v>49</v>
       </c>
       <c r="I11" t="s">
         <v>18</v>
       </c>
       <c r="J11" s="2">
-        <v>46308.291666666664</v>
+        <v>46309.104166666664</v>
       </c>
       <c r="K11" s="2">
-        <v>46309.75</v>
+        <v>46309.916666666664</v>
       </c>
       <c r="L11" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -1548,7 +1545,7 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="C12" t="s">
         <v>50</v>
@@ -1563,22 +1560,19 @@
         <v>53</v>
       </c>
       <c r="G12" t="s">
-        <v>53</v>
-      </c>
-      <c r="H12" t="s">
+        <v>17</v>
+      </c>
+      <c r="I12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J12" s="2">
+        <v>46309.208333333336</v>
+      </c>
+      <c r="K12" s="2">
+        <v>46310.75</v>
+      </c>
+      <c r="L12" t="s">
         <v>54</v>
-      </c>
-      <c r="I12" t="s">
-        <v>18</v>
-      </c>
-      <c r="J12" s="2">
-        <v>46309.104166666664</v>
-      </c>
-      <c r="K12" s="2">
-        <v>46309.916666666664</v>
-      </c>
-      <c r="L12" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -1586,10 +1580,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="C13" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="D13" t="s">
         <v>56</v>
@@ -1604,16 +1598,16 @@
         <v>17</v>
       </c>
       <c r="I13" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J13" s="2">
-        <v>46309.208333333336</v>
+        <v>46309.25</v>
       </c>
       <c r="K13" s="2">
-        <v>46310.75</v>
+        <v>46309.708333333336</v>
       </c>
       <c r="L13" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -1621,19 +1615,19 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C14" t="s">
         <v>21</v>
       </c>
       <c r="D14" t="s">
+        <v>59</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>61</v>
-      </c>
       <c r="F14" t="s">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="G14" t="s">
         <v>17</v>
@@ -1642,10 +1636,10 @@
         <v>25</v>
       </c>
       <c r="J14" s="2">
-        <v>46309.25</v>
+        <v>46309.541666666664</v>
       </c>
       <c r="K14" s="2">
-        <v>46309.708333333336</v>
+        <v>46310.041666666664</v>
       </c>
       <c r="L14" t="s">
         <v>26</v>
@@ -1653,34 +1647,34 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B15" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C15" t="s">
         <v>21</v>
       </c>
       <c r="D15" t="s">
+        <v>62</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="F15" t="s">
         <v>64</v>
-      </c>
-      <c r="F15" t="s">
-        <v>23</v>
       </c>
       <c r="G15" t="s">
         <v>17</v>
       </c>
       <c r="I15" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J15" s="2">
-        <v>46309.541666666664</v>
+        <v>46309.625</v>
       </c>
       <c r="K15" s="2">
-        <v>46310.041666666664</v>
+        <v>46311.75</v>
       </c>
       <c r="L15" t="s">
         <v>26</v>
@@ -1688,37 +1682,40 @@
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="C16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D16" t="s">
-        <v>66</v>
-      </c>
-      <c r="E16" s="1" t="s">
         <v>67</v>
+      </c>
+      <c r="E16" s="1">
+        <v>26165</v>
       </c>
       <c r="F16" t="s">
         <v>68</v>
       </c>
       <c r="G16" t="s">
-        <v>17</v>
+        <v>69</v>
+      </c>
+      <c r="H16" t="s">
+        <v>69</v>
       </c>
       <c r="I16" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="J16" s="2">
         <v>46309.625</v>
       </c>
       <c r="K16" s="2">
-        <v>46311.75</v>
+        <v>46310.041666666664</v>
       </c>
       <c r="L16" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1726,37 +1723,34 @@
         <v>12</v>
       </c>
       <c r="B17" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C17" t="s">
-        <v>70</v>
+        <v>21</v>
       </c>
       <c r="D17" t="s">
-        <v>71</v>
-      </c>
-      <c r="E17" s="1">
-        <v>26165</v>
+        <v>56</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>57</v>
       </c>
       <c r="F17" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="G17" t="s">
-        <v>73</v>
-      </c>
-      <c r="H17" t="s">
-        <v>73</v>
+        <v>17</v>
       </c>
       <c r="I17" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="J17" s="2">
-        <v>46309.625</v>
+        <v>46309.75</v>
       </c>
       <c r="K17" s="2">
-        <v>46310.041666666664</v>
+        <v>46310.666666666664</v>
       </c>
       <c r="L17" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -1764,31 +1758,34 @@
         <v>12</v>
       </c>
       <c r="B18" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="C18" t="s">
         <v>21</v>
       </c>
       <c r="D18" t="s">
-        <v>60</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>61</v>
+        <v>72</v>
+      </c>
+      <c r="E18" s="1">
+        <v>4</v>
       </c>
       <c r="F18" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="G18" t="s">
-        <v>17</v>
+        <v>24</v>
+      </c>
+      <c r="H18" t="s">
+        <v>74</v>
       </c>
       <c r="I18" t="s">
         <v>25</v>
       </c>
       <c r="J18" s="2">
-        <v>46309.75</v>
+        <v>46310.25</v>
       </c>
       <c r="K18" s="2">
-        <v>46310.666666666664</v>
+        <v>46310.75</v>
       </c>
       <c r="L18" t="s">
         <v>26</v>
@@ -1796,40 +1793,37 @@
     </row>
     <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B19" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C19" t="s">
-        <v>21</v>
+        <v>75</v>
       </c>
       <c r="D19" t="s">
         <v>76</v>
       </c>
-      <c r="E19" s="1">
-        <v>4</v>
+      <c r="E19" s="1" t="s">
+        <v>77</v>
       </c>
       <c r="F19" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G19" t="s">
-        <v>24</v>
-      </c>
-      <c r="H19" t="s">
-        <v>78</v>
+        <v>17</v>
       </c>
       <c r="I19" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J19" s="2">
         <v>46310.25</v>
       </c>
       <c r="K19" s="2">
-        <v>46310.75</v>
+        <v>46311.166666666664</v>
       </c>
       <c r="L19" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -1837,7 +1831,7 @@
         <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="C20" t="s">
         <v>79</v>
@@ -1852,7 +1846,7 @@
         <v>82</v>
       </c>
       <c r="G20" t="s">
-        <v>17</v>
+        <v>83</v>
       </c>
       <c r="I20" t="s">
         <v>18</v>
@@ -1861,10 +1855,10 @@
         <v>46310.25</v>
       </c>
       <c r="K20" s="2">
-        <v>46311.166666666664</v>
+        <v>46311.708333333336</v>
       </c>
       <c r="L20" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -1872,145 +1866,145 @@
         <v>27</v>
       </c>
       <c r="B21" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C21" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D21" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F21" t="s">
-        <v>86</v>
+        <v>31</v>
       </c>
       <c r="G21" t="s">
-        <v>87</v>
+        <v>17</v>
       </c>
       <c r="I21" t="s">
         <v>18</v>
       </c>
       <c r="J21" s="2">
-        <v>46310.25</v>
+        <v>46310.291666666664</v>
       </c>
       <c r="K21" s="2">
-        <v>46311.708333333336</v>
+        <v>46311.166666666664</v>
       </c>
       <c r="L21" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22" spans="1:12">
       <c r="A22" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B22" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="C22" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D22" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>89</v>
+        <v>47</v>
       </c>
       <c r="F22" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="G22" t="s">
-        <v>17</v>
+        <v>48</v>
+      </c>
+      <c r="H22" t="s">
+        <v>49</v>
       </c>
       <c r="I22" t="s">
         <v>18</v>
       </c>
       <c r="J22" s="2">
-        <v>46310.291666666664</v>
+        <v>46311.104166666664</v>
       </c>
       <c r="K22" s="2">
-        <v>46311.166666666664</v>
+        <v>46311.916666666664</v>
       </c>
       <c r="L22" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23" spans="1:12">
       <c r="A23" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B23" t="s">
+        <v>61</v>
+      </c>
+      <c r="C23" t="s">
+        <v>88</v>
+      </c>
+      <c r="D23" t="s">
+        <v>89</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F23" t="s">
+        <v>91</v>
+      </c>
+      <c r="G23" t="s">
+        <v>24</v>
+      </c>
+      <c r="H23" t="s">
         <v>49</v>
       </c>
-      <c r="C23" t="s">
-        <v>50</v>
-      </c>
-      <c r="D23" t="s">
-        <v>90</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="F23" t="s">
-        <v>53</v>
-      </c>
-      <c r="G23" t="s">
-        <v>53</v>
-      </c>
-      <c r="H23" t="s">
-        <v>54</v>
-      </c>
       <c r="I23" t="s">
         <v>18</v>
       </c>
       <c r="J23" s="2">
-        <v>46311.104166666664</v>
+        <v>46311.25</v>
       </c>
       <c r="K23" s="2">
-        <v>46311.916666666664</v>
+        <v>46312.166666666664</v>
       </c>
       <c r="L23" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B24" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C24" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D24" t="s">
-        <v>92</v>
-      </c>
-      <c r="E24" s="1" t="s">
         <v>93</v>
       </c>
       <c r="F24" t="s">
-        <v>94</v>
+        <v>48</v>
       </c>
       <c r="G24" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="H24" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="I24" t="s">
         <v>18</v>
       </c>
       <c r="J24" s="2">
-        <v>46311.25</v>
+        <v>46311.291666666664</v>
       </c>
       <c r="K24" s="2">
-        <v>46312.166666666664</v>
+        <v>46312.125</v>
       </c>
       <c r="L24" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:12">
@@ -2018,34 +2012,37 @@
         <v>12</v>
       </c>
       <c r="B25" t="s">
+        <v>71</v>
+      </c>
+      <c r="C25" t="s">
+        <v>21</v>
+      </c>
+      <c r="D25" t="s">
+        <v>94</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="F25" t="s">
+        <v>23</v>
+      </c>
+      <c r="G25" t="s">
+        <v>17</v>
+      </c>
+      <c r="H25" t="s">
         <v>49</v>
       </c>
-      <c r="C25" t="s">
-        <v>95</v>
-      </c>
-      <c r="D25" t="s">
+      <c r="I25" t="s">
         <v>96</v>
       </c>
-      <c r="F25" t="s">
-        <v>53</v>
-      </c>
-      <c r="G25" t="s">
-        <v>53</v>
-      </c>
-      <c r="H25" t="s">
-        <v>54</v>
-      </c>
-      <c r="I25" t="s">
-        <v>18</v>
-      </c>
       <c r="J25" s="2">
-        <v>46311.291666666664</v>
+        <v>46311.541666666664</v>
       </c>
       <c r="K25" s="2">
-        <v>46312.125</v>
+        <v>46312.083333333336</v>
       </c>
       <c r="L25" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -2053,37 +2050,37 @@
         <v>12</v>
       </c>
       <c r="B26" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="C26" t="s">
-        <v>21</v>
+        <v>97</v>
       </c>
       <c r="D26" t="s">
-        <v>97</v>
-      </c>
-      <c r="E26" s="1" t="s">
         <v>98</v>
       </c>
+      <c r="E26" s="1">
+        <v>26164</v>
+      </c>
       <c r="F26" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="G26" t="s">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="H26" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="I26" t="s">
-        <v>99</v>
+        <v>70</v>
       </c>
       <c r="J26" s="2">
-        <v>46311.541666666664</v>
+        <v>46311.625</v>
       </c>
       <c r="K26" s="2">
-        <v>46312.083333333336</v>
+        <v>46312.041666666664</v>
       </c>
       <c r="L26" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -2091,34 +2088,37 @@
         <v>12</v>
       </c>
       <c r="B27" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="C27" t="s">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="D27" t="s">
-        <v>101</v>
-      </c>
-      <c r="E27" s="1">
-        <v>26164</v>
+        <v>94</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="F27" t="s">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="G27" t="s">
-        <v>73</v>
+        <v>17</v>
       </c>
       <c r="H27" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="I27" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="J27" s="2">
-        <v>46311.625</v>
+        <v>46312.125</v>
       </c>
       <c r="K27" s="2">
-        <v>46312.041666666664</v>
+        <v>46312.666666666664</v>
+      </c>
+      <c r="L27" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="28" spans="1:12">
@@ -2126,57 +2126,54 @@
         <v>12</v>
       </c>
       <c r="B28" t="s">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="C28" t="s">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="D28" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F28" t="s">
-        <v>23</v>
+        <v>102</v>
       </c>
       <c r="G28" t="s">
         <v>17</v>
       </c>
-      <c r="H28" t="s">
-        <v>54</v>
-      </c>
       <c r="I28" t="s">
-        <v>99</v>
+        <v>18</v>
       </c>
       <c r="J28" s="2">
-        <v>46312.125</v>
+        <v>46312.5</v>
       </c>
       <c r="K28" s="2">
-        <v>46312.666666666664</v>
+        <v>46315.75</v>
       </c>
       <c r="L28" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29" spans="1:12">
       <c r="A29" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>13</v>
+        <v>61</v>
       </c>
       <c r="C29" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D29" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F29" t="s">
-        <v>105</v>
+        <v>64</v>
       </c>
       <c r="G29" t="s">
         <v>17</v>
@@ -2185,13 +2182,13 @@
         <v>18</v>
       </c>
       <c r="J29" s="2">
-        <v>46312.5</v>
+        <v>46312.625</v>
       </c>
       <c r="K29" s="2">
-        <v>46315.75</v>
+        <v>46314.75</v>
       </c>
       <c r="L29" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="30" spans="1:12">
@@ -2199,22 +2196,22 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="C30" t="s">
-        <v>65</v>
+        <v>106</v>
       </c>
       <c r="D30" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F30" t="s">
-        <v>68</v>
+        <v>109</v>
       </c>
       <c r="G30" t="s">
-        <v>17</v>
+        <v>110</v>
       </c>
       <c r="I30" t="s">
         <v>18</v>
@@ -2223,45 +2220,45 @@
         <v>46312.625</v>
       </c>
       <c r="K30" s="2">
-        <v>46314.75</v>
+        <v>46313.75</v>
       </c>
       <c r="L30" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="31" spans="1:12">
       <c r="A31" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B31" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="C31" t="s">
-        <v>108</v>
+        <v>21</v>
       </c>
       <c r="D31" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F31" t="s">
-        <v>111</v>
+        <v>23</v>
       </c>
       <c r="G31" t="s">
-        <v>112</v>
+        <v>17</v>
       </c>
       <c r="I31" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J31" s="2">
-        <v>46312.625</v>
+        <v>46314.25</v>
       </c>
       <c r="K31" s="2">
-        <v>46313.75</v>
+        <v>46314.75</v>
       </c>
       <c r="L31" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
     <row r="32" spans="1:12">
@@ -2269,7 +2266,7 @@
         <v>12</v>
       </c>
       <c r="B32" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C32" t="s">
         <v>21</v>
@@ -2277,11 +2274,11 @@
       <c r="D32" t="s">
         <v>113</v>
       </c>
-      <c r="E32" s="1" t="s">
-        <v>114</v>
+      <c r="E32" s="1">
+        <v>2</v>
       </c>
       <c r="F32" t="s">
-        <v>115</v>
+        <v>58</v>
       </c>
       <c r="G32" t="s">
         <v>17</v>
@@ -2304,19 +2301,19 @@
         <v>12</v>
       </c>
       <c r="B33" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C33" t="s">
         <v>21</v>
       </c>
       <c r="D33" t="s">
+        <v>114</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F33" t="s">
         <v>116</v>
-      </c>
-      <c r="E33" s="1">
-        <v>2</v>
-      </c>
-      <c r="F33" t="s">
-        <v>62</v>
       </c>
       <c r="G33" t="s">
         <v>17</v>
@@ -2339,16 +2336,16 @@
         <v>12</v>
       </c>
       <c r="B34" t="s">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="C34" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D34" t="s">
         <v>117</v>
       </c>
-      <c r="E34" s="1" t="s">
-        <v>118</v>
+      <c r="E34" s="1">
+        <v>34</v>
       </c>
       <c r="F34" t="s">
         <v>23</v>
@@ -2357,16 +2354,16 @@
         <v>17</v>
       </c>
       <c r="I34" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J34" s="2">
-        <v>46314.25</v>
+        <v>46314.625</v>
       </c>
       <c r="K34" s="2">
-        <v>46314.75</v>
+        <v>46318.75</v>
       </c>
       <c r="L34" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
     </row>
     <row r="35" spans="1:12">
@@ -2374,22 +2371,22 @@
         <v>27</v>
       </c>
       <c r="B35" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="D35" t="s">
+        <v>118</v>
+      </c>
+      <c r="E35" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="E35" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="F35" t="s">
-        <v>43</v>
+        <v>120</v>
       </c>
       <c r="G35" t="s">
         <v>17</v>
       </c>
       <c r="H35" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="I35" t="s">
         <v>18</v>
@@ -2401,7 +2398,7 @@
         <v>46315.166666666664</v>
       </c>
       <c r="L35" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="36" spans="1:12">
@@ -2409,34 +2406,34 @@
         <v>12</v>
       </c>
       <c r="B36" t="s">
-        <v>13</v>
+        <v>121</v>
       </c>
       <c r="C36" t="s">
-        <v>14</v>
+        <v>122</v>
       </c>
       <c r="D36" t="s">
-        <v>120</v>
-      </c>
-      <c r="E36" s="1">
-        <v>34</v>
+        <v>123</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>124</v>
       </c>
       <c r="F36" t="s">
-        <v>23</v>
+        <v>125</v>
       </c>
       <c r="G36" t="s">
-        <v>17</v>
+        <v>126</v>
       </c>
       <c r="I36" t="s">
         <v>18</v>
       </c>
       <c r="J36" s="2">
-        <v>46314.625</v>
+        <v>46315.208333333336</v>
       </c>
       <c r="K36" s="2">
-        <v>46318.75</v>
+        <v>46316.791666666664</v>
       </c>
       <c r="L36" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="37" spans="1:12">
@@ -2444,69 +2441,69 @@
         <v>12</v>
       </c>
       <c r="B37" t="s">
-        <v>121</v>
+        <v>35</v>
       </c>
       <c r="C37" t="s">
-        <v>122</v>
+        <v>36</v>
       </c>
       <c r="D37" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F37" t="s">
-        <v>125</v>
+        <v>16</v>
       </c>
       <c r="G37" t="s">
-        <v>126</v>
+        <v>24</v>
       </c>
       <c r="I37" t="s">
         <v>18</v>
       </c>
       <c r="J37" s="2">
-        <v>46315.208333333336</v>
+        <v>46315.25</v>
       </c>
       <c r="K37" s="2">
-        <v>46316.791666666664</v>
+        <v>46317.166666666664</v>
       </c>
       <c r="L37" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="38" spans="1:12">
       <c r="A38" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B38" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C38" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D38" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F38" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="G38" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="I38" t="s">
         <v>18</v>
       </c>
       <c r="J38" s="2">
-        <v>46315.25</v>
+        <v>46315.291666666664</v>
       </c>
       <c r="K38" s="2">
         <v>46317.166666666664</v>
       </c>
       <c r="L38" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="39" spans="1:12">
@@ -2520,10 +2517,10 @@
         <v>32</v>
       </c>
       <c r="D39" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F39" t="s">
         <v>31</v>
@@ -2535,48 +2532,51 @@
         <v>18</v>
       </c>
       <c r="J39" s="2">
-        <v>46315.291666666664</v>
+        <v>46315.708333333336</v>
       </c>
       <c r="K39" s="2">
-        <v>46317.166666666664</v>
+        <v>46317.75</v>
       </c>
       <c r="L39" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="40" spans="1:12">
       <c r="A40" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B40" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="C40" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="D40" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F40" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="G40" t="s">
-        <v>17</v>
+        <v>48</v>
+      </c>
+      <c r="H40" t="s">
+        <v>49</v>
       </c>
       <c r="I40" t="s">
         <v>18</v>
       </c>
       <c r="J40" s="2">
-        <v>46315.708333333336</v>
+        <v>46316.104166666664</v>
       </c>
       <c r="K40" s="2">
-        <v>46317.75</v>
+        <v>46316.916666666664</v>
       </c>
       <c r="L40" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="41" spans="1:12">
@@ -2584,34 +2584,31 @@
         <v>12</v>
       </c>
       <c r="B41" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="C41" t="s">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="D41" t="s">
-        <v>133</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
+      </c>
+      <c r="E41" s="1">
+        <v>63</v>
       </c>
       <c r="F41" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="G41" t="s">
-        <v>53</v>
-      </c>
-      <c r="H41" t="s">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="I41" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J41" s="2">
-        <v>46316.104166666664</v>
+        <v>46316.25</v>
       </c>
       <c r="K41" s="2">
-        <v>46316.916666666664</v>
+        <v>46316.75</v>
       </c>
       <c r="L41" t="s">
         <v>26</v>
@@ -2622,22 +2619,25 @@
         <v>12</v>
       </c>
       <c r="B42" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="C42" t="s">
         <v>21</v>
       </c>
       <c r="D42" t="s">
-        <v>135</v>
-      </c>
-      <c r="E42" s="1">
-        <v>63</v>
+        <v>136</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>137</v>
       </c>
       <c r="F42" t="s">
-        <v>23</v>
+        <v>116</v>
       </c>
       <c r="G42" t="s">
-        <v>24</v>
+        <v>17</v>
+      </c>
+      <c r="H42" t="s">
+        <v>138</v>
       </c>
       <c r="I42" t="s">
         <v>25</v>
@@ -2657,37 +2657,37 @@
         <v>12</v>
       </c>
       <c r="B43" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C43" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="D43" t="s">
-        <v>136</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>137</v>
+        <v>67</v>
+      </c>
+      <c r="E43" s="1">
+        <v>26169</v>
       </c>
       <c r="F43" t="s">
-        <v>115</v>
+        <v>68</v>
       </c>
       <c r="G43" t="s">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="H43" t="s">
-        <v>138</v>
+        <v>69</v>
       </c>
       <c r="I43" t="s">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="J43" s="2">
-        <v>46316.25</v>
+        <v>46316.625</v>
       </c>
       <c r="K43" s="2">
-        <v>46316.75</v>
+        <v>46317.041666666664</v>
       </c>
       <c r="L43" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
     </row>
     <row r="44" spans="1:12">
@@ -2698,7 +2698,7 @@
         <v>13</v>
       </c>
       <c r="C44" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D44" t="s">
         <v>139</v>
@@ -2707,7 +2707,7 @@
         <v>140</v>
       </c>
       <c r="F44" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="G44" t="s">
         <v>17</v>
@@ -2722,7 +2722,7 @@
         <v>46319.75</v>
       </c>
       <c r="L44" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="45" spans="1:12">
@@ -2730,37 +2730,34 @@
         <v>12</v>
       </c>
       <c r="B45" t="s">
-        <v>69</v>
+        <v>13</v>
       </c>
       <c r="C45" t="s">
-        <v>70</v>
+        <v>99</v>
       </c>
       <c r="D45" t="s">
-        <v>71</v>
-      </c>
-      <c r="E45" s="1">
-        <v>26169</v>
+        <v>139</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>140</v>
       </c>
       <c r="F45" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="G45" t="s">
-        <v>73</v>
-      </c>
-      <c r="H45" t="s">
-        <v>73</v>
+        <v>17</v>
       </c>
       <c r="I45" t="s">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="J45" s="2">
         <v>46316.625</v>
       </c>
       <c r="K45" s="2">
-        <v>46317.041666666664</v>
+        <v>46319.75</v>
       </c>
       <c r="L45" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="46" spans="1:12">
@@ -2768,34 +2765,37 @@
         <v>12</v>
       </c>
       <c r="B46" t="s">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="C46" t="s">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="D46" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F46" t="s">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="G46" t="s">
         <v>17</v>
       </c>
+      <c r="H46" t="s">
+        <v>138</v>
+      </c>
       <c r="I46" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J46" s="2">
-        <v>46316.625</v>
+        <v>46316.791666666664</v>
       </c>
       <c r="K46" s="2">
-        <v>46319.75</v>
+        <v>46317.75</v>
       </c>
       <c r="L46" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
     <row r="47" spans="1:12">
@@ -2803,69 +2803,66 @@
         <v>12</v>
       </c>
       <c r="B47" t="s">
-        <v>75</v>
-      </c>
-      <c r="C47" t="s">
-        <v>21</v>
+        <v>121</v>
       </c>
       <c r="D47" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F47" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="G47" t="s">
-        <v>17</v>
-      </c>
-      <c r="H47" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="I47" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J47" s="2">
-        <v>46316.791666666664</v>
+        <v>46317.208333333336</v>
       </c>
       <c r="K47" s="2">
-        <v>46317.75</v>
+        <v>46318.708333333336</v>
       </c>
       <c r="L47" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
     </row>
     <row r="48" spans="1:12">
       <c r="A48" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B48" t="s">
-        <v>121</v>
+        <v>61</v>
+      </c>
+      <c r="C48" t="s">
+        <v>106</v>
       </c>
       <c r="D48" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F48" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="G48" t="s">
-        <v>144</v>
+        <v>110</v>
       </c>
       <c r="I48" t="s">
         <v>18</v>
       </c>
       <c r="J48" s="2">
-        <v>46317.208333333336</v>
+        <v>46317.25</v>
       </c>
       <c r="K48" s="2">
-        <v>46318.708333333336</v>
+        <v>46318.166666666664</v>
       </c>
       <c r="L48" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="49" spans="1:12">
@@ -2873,34 +2870,31 @@
         <v>27</v>
       </c>
       <c r="B49" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C49" t="s">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="D49" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F49" t="s">
-        <v>111</v>
-      </c>
-      <c r="G49" t="s">
-        <v>112</v>
+        <v>31</v>
       </c>
       <c r="I49" t="s">
         <v>18</v>
       </c>
       <c r="J49" s="2">
-        <v>46317.25</v>
+        <v>46317.291666666664</v>
       </c>
       <c r="K49" s="2">
         <v>46318.166666666664</v>
       </c>
       <c r="L49" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="50" spans="1:12">
@@ -2908,63 +2902,66 @@
         <v>27</v>
       </c>
       <c r="B50" t="s">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="C50" t="s">
-        <v>46</v>
+        <v>149</v>
       </c>
       <c r="D50" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="F50" t="s">
-        <v>31</v>
+        <v>82</v>
       </c>
       <c r="I50" t="s">
         <v>18</v>
       </c>
       <c r="J50" s="2">
-        <v>46317.291666666664</v>
+        <v>46317.927777777775</v>
       </c>
       <c r="K50" s="2">
-        <v>46318.166666666664</v>
+        <v>46318.969444444447</v>
       </c>
       <c r="L50" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="51" spans="1:12">
       <c r="A51" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B51" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="C51" t="s">
-        <v>149</v>
+        <v>21</v>
       </c>
       <c r="D51" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F51" t="s">
-        <v>86</v>
+        <v>23</v>
+      </c>
+      <c r="G51" t="s">
+        <v>17</v>
       </c>
       <c r="I51" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J51" s="2">
-        <v>46317.927777777775</v>
+        <v>46318.25</v>
       </c>
       <c r="K51" s="2">
-        <v>46318.969444444447</v>
+        <v>46318.75</v>
       </c>
       <c r="L51" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
     <row r="52" spans="1:12">
@@ -2972,19 +2969,19 @@
         <v>12</v>
       </c>
       <c r="B52" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C52" t="s">
         <v>21</v>
       </c>
       <c r="D52" t="s">
-        <v>152</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
+      </c>
+      <c r="E52" s="1">
+        <v>4</v>
       </c>
       <c r="F52" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="G52" t="s">
         <v>17</v>
@@ -3007,60 +3004,57 @@
         <v>12</v>
       </c>
       <c r="B53" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="C53" t="s">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="D53" t="s">
-        <v>154</v>
-      </c>
-      <c r="E53" s="1">
-        <v>4</v>
+        <v>155</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>156</v>
       </c>
       <c r="F53" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="G53" t="s">
-        <v>17</v>
+        <v>48</v>
+      </c>
+      <c r="H53" t="s">
+        <v>49</v>
       </c>
       <c r="I53" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J53" s="2">
-        <v>46318.25</v>
+        <v>46318.291666666664</v>
       </c>
       <c r="K53" s="2">
-        <v>46318.75</v>
+        <v>46319.125</v>
       </c>
       <c r="L53" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
     </row>
     <row r="54" spans="1:12">
       <c r="A54" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B54" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="C54" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="D54" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F54" t="s">
-        <v>53</v>
-      </c>
-      <c r="G54" t="s">
-        <v>53</v>
-      </c>
-      <c r="H54" t="s">
-        <v>54</v>
+        <v>91</v>
       </c>
       <c r="I54" t="s">
         <v>18</v>
@@ -3069,10 +3063,10 @@
         <v>46318.291666666664</v>
       </c>
       <c r="K54" s="2">
-        <v>46319.125</v>
+        <v>46319.666666666664</v>
       </c>
       <c r="L54" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
     </row>
     <row r="55" spans="1:12">
@@ -3080,10 +3074,10 @@
         <v>27</v>
       </c>
       <c r="B55" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="C55" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D55" t="s">
         <v>157</v>
@@ -3092,7 +3086,7 @@
         <v>158</v>
       </c>
       <c r="F55" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="I55" t="s">
         <v>18</v>
@@ -3104,39 +3098,45 @@
         <v>46319.666666666664</v>
       </c>
       <c r="L55" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="56" spans="1:12">
       <c r="A56" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B56" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="C56" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D56" t="s">
-        <v>157</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>158</v>
+        <v>98</v>
+      </c>
+      <c r="E56" s="1">
+        <v>26168</v>
       </c>
       <c r="F56" t="s">
-        <v>94</v>
+        <v>68</v>
+      </c>
+      <c r="G56" t="s">
+        <v>69</v>
+      </c>
+      <c r="H56" t="s">
+        <v>69</v>
       </c>
       <c r="I56" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="J56" s="2">
-        <v>46318.291666666664</v>
+        <v>46318.625</v>
       </c>
       <c r="K56" s="2">
-        <v>46319.666666666664</v>
+        <v>46319.041666666664</v>
       </c>
       <c r="L56" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="57" spans="1:12">
@@ -3144,34 +3144,31 @@
         <v>12</v>
       </c>
       <c r="B57" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="C57" t="s">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="D57" t="s">
-        <v>101</v>
-      </c>
-      <c r="E57" s="1">
-        <v>26168</v>
+        <v>159</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>156</v>
       </c>
       <c r="F57" t="s">
-        <v>72</v>
-      </c>
-      <c r="G57" t="s">
-        <v>73</v>
-      </c>
-      <c r="H57" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="I57" t="s">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="J57" s="2">
-        <v>46318.625</v>
+        <v>46318.704861111109</v>
       </c>
       <c r="K57" s="2">
-        <v>46319.041666666664</v>
+        <v>46319.204861111109</v>
+      </c>
+      <c r="L57" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="58" spans="1:12">
@@ -3179,31 +3176,34 @@
         <v>12</v>
       </c>
       <c r="B58" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="C58" t="s">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="D58" t="s">
-        <v>159</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>156</v>
+        <v>160</v>
+      </c>
+      <c r="E58" s="1">
+        <v>1</v>
       </c>
       <c r="F58" t="s">
-        <v>53</v>
+        <v>161</v>
+      </c>
+      <c r="G58" t="s">
+        <v>17</v>
       </c>
       <c r="I58" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J58" s="2">
-        <v>46318.704861111109</v>
+        <v>46319.25</v>
       </c>
       <c r="K58" s="2">
-        <v>46319.204861111109</v>
+        <v>46322.75</v>
       </c>
       <c r="L58" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
     <row r="59" spans="1:12">
@@ -3211,19 +3211,19 @@
         <v>12</v>
       </c>
       <c r="B59" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C59" t="s">
         <v>21</v>
       </c>
       <c r="D59" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F59" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G59" t="s">
         <v>17</v>
@@ -3246,98 +3246,98 @@
         <v>12</v>
       </c>
       <c r="B60" t="s">
-        <v>20</v>
+        <v>121</v>
       </c>
       <c r="C60" t="s">
-        <v>21</v>
+        <v>122</v>
       </c>
       <c r="D60" t="s">
-        <v>162</v>
-      </c>
-      <c r="E60" s="1">
-        <v>1</v>
+        <v>164</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>165</v>
       </c>
       <c r="F60" t="s">
-        <v>163</v>
-      </c>
-      <c r="G60" t="s">
-        <v>17</v>
+        <v>125</v>
       </c>
       <c r="I60" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J60" s="2">
-        <v>46319.25</v>
+        <v>46320</v>
       </c>
       <c r="K60" s="2">
-        <v>46322.75</v>
+        <v>46322</v>
       </c>
       <c r="L60" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
     </row>
     <row r="61" spans="1:12">
       <c r="A61" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B61" t="s">
-        <v>121</v>
+        <v>61</v>
       </c>
       <c r="C61" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="D61" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F61" t="s">
-        <v>125</v>
+        <v>64</v>
       </c>
       <c r="I61" t="s">
         <v>18</v>
       </c>
       <c r="J61" s="2">
-        <v>46320</v>
+        <v>46320.21875</v>
       </c>
       <c r="K61" s="2">
-        <v>46322</v>
+        <v>46324.59375</v>
       </c>
       <c r="L61" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="62" spans="1:12">
       <c r="A62" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B62" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C62" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="D62" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F62" t="s">
-        <v>68</v>
+        <v>16</v>
+      </c>
+      <c r="G62" t="s">
+        <v>24</v>
       </c>
       <c r="I62" t="s">
         <v>18</v>
       </c>
       <c r="J62" s="2">
-        <v>46320.21875</v>
+        <v>46321.208333333336</v>
       </c>
       <c r="K62" s="2">
-        <v>46324.59375</v>
+        <v>46323.166666666664</v>
       </c>
       <c r="L62" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="63" spans="1:12">
@@ -3351,10 +3351,10 @@
         <v>32</v>
       </c>
       <c r="D63" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F63" t="s">
         <v>31</v>
@@ -3363,13 +3363,13 @@
         <v>18</v>
       </c>
       <c r="J63" s="2">
-        <v>46320.649305555555</v>
+        <v>46321.21875</v>
       </c>
       <c r="K63" s="2">
-        <v>46321.149305555555</v>
+        <v>46323.21875</v>
       </c>
       <c r="L63" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="64" spans="1:12">
@@ -3377,16 +3377,16 @@
         <v>12</v>
       </c>
       <c r="B64" t="s">
+        <v>35</v>
+      </c>
+      <c r="C64" t="s">
         <v>36</v>
       </c>
-      <c r="C64" t="s">
-        <v>55</v>
-      </c>
       <c r="D64" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F64" t="s">
         <v>16</v>
@@ -3398,13 +3398,13 @@
         <v>18</v>
       </c>
       <c r="J64" s="2">
-        <v>46321.208333333336</v>
+        <v>46321.25</v>
       </c>
       <c r="K64" s="2">
         <v>46323.166666666664</v>
       </c>
       <c r="L64" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="65" spans="1:12">
@@ -3412,34 +3412,34 @@
         <v>12</v>
       </c>
       <c r="B65" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="C65" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="D65" t="s">
-        <v>172</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
+      </c>
+      <c r="E65" s="1">
+        <v>21</v>
       </c>
       <c r="F65" t="s">
         <v>16</v>
       </c>
       <c r="G65" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="I65" t="s">
         <v>18</v>
       </c>
       <c r="J65" s="2">
-        <v>46321.25</v>
+        <v>46321.625</v>
       </c>
       <c r="K65" s="2">
-        <v>46323.166666666664</v>
+        <v>46325.75</v>
       </c>
       <c r="L65" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="66" spans="1:12">
@@ -3447,95 +3447,95 @@
         <v>12</v>
       </c>
       <c r="B66" t="s">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="C66" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D66" t="s">
-        <v>174</v>
-      </c>
-      <c r="E66" s="1">
-        <v>21</v>
+        <v>175</v>
       </c>
       <c r="F66" t="s">
-        <v>16</v>
+        <v>73</v>
       </c>
       <c r="G66" t="s">
-        <v>17</v>
+        <v>24</v>
+      </c>
+      <c r="H66" t="s">
+        <v>74</v>
       </c>
       <c r="I66" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J66" s="2">
-        <v>46321.625</v>
+        <v>46322.25</v>
       </c>
       <c r="K66" s="2">
-        <v>46325.75</v>
+        <v>46322.75</v>
       </c>
       <c r="L66" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
     <row r="67" spans="1:12">
       <c r="A67" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B67" t="s">
-        <v>75</v>
-      </c>
-      <c r="C67" t="s">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="D67" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F67" t="s">
-        <v>77</v>
-      </c>
-      <c r="G67" t="s">
-        <v>24</v>
-      </c>
-      <c r="H67" t="s">
-        <v>78</v>
+        <v>120</v>
       </c>
       <c r="I67" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J67" s="2">
-        <v>46322.25</v>
+        <v>46322.256249999999</v>
       </c>
       <c r="K67" s="2">
-        <v>46322.75</v>
+        <v>46323.381249999999</v>
       </c>
       <c r="L67" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
     </row>
     <row r="68" spans="1:12">
       <c r="A68" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B68" t="s">
-        <v>40</v>
+        <v>55</v>
+      </c>
+      <c r="C68" t="s">
+        <v>21</v>
       </c>
       <c r="D68" t="s">
-        <v>176</v>
+        <v>177</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>178</v>
       </c>
       <c r="F68" t="s">
-        <v>43</v>
+        <v>23</v>
+      </c>
+      <c r="G68" t="s">
+        <v>17</v>
       </c>
       <c r="I68" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J68" s="2">
-        <v>46322.256249999999</v>
+        <v>46323.25</v>
       </c>
       <c r="K68" s="2">
-        <v>46323.381249999999</v>
+        <v>46323.75</v>
       </c>
       <c r="L68" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
     <row r="69" spans="1:12">
@@ -3543,31 +3543,28 @@
         <v>12</v>
       </c>
       <c r="B69" t="s">
-        <v>121</v>
+        <v>44</v>
       </c>
       <c r="C69" t="s">
-        <v>122</v>
+        <v>45</v>
       </c>
       <c r="D69" t="s">
-        <v>177</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>178</v>
+        <v>87</v>
       </c>
       <c r="F69" t="s">
-        <v>125</v>
+        <v>48</v>
       </c>
       <c r="I69" t="s">
         <v>18</v>
       </c>
       <c r="J69" s="2">
-        <v>46322.388194444444</v>
+        <v>46323.291666666664</v>
       </c>
       <c r="K69" s="2">
-        <v>46325.388194444444</v>
+        <v>46323.791666666664</v>
       </c>
       <c r="L69" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="70" spans="1:12">
@@ -3575,10 +3572,10 @@
         <v>12</v>
       </c>
       <c r="B70" t="s">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="C70" t="s">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="D70" t="s">
         <v>179</v>
@@ -3587,22 +3584,19 @@
         <v>180</v>
       </c>
       <c r="F70" t="s">
-        <v>23</v>
-      </c>
-      <c r="G70" t="s">
-        <v>17</v>
+        <v>181</v>
       </c>
       <c r="I70" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J70" s="2">
-        <v>46323.25</v>
+        <v>46323.622916666667</v>
       </c>
       <c r="K70" s="2">
-        <v>46323.75</v>
+        <v>46324.875</v>
       </c>
       <c r="L70" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
     </row>
     <row r="71" spans="1:12">
@@ -3610,28 +3604,37 @@
         <v>12</v>
       </c>
       <c r="B71" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="C71" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="D71" t="s">
-        <v>90</v>
+        <v>67</v>
+      </c>
+      <c r="E71" s="1">
+        <v>26173</v>
       </c>
       <c r="F71" t="s">
-        <v>53</v>
+        <v>68</v>
+      </c>
+      <c r="G71" t="s">
+        <v>69</v>
+      </c>
+      <c r="H71" t="s">
+        <v>69</v>
       </c>
       <c r="I71" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="J71" s="2">
-        <v>46323.291666666664</v>
+        <v>46323.625</v>
       </c>
       <c r="K71" s="2">
-        <v>46323.791666666664</v>
+        <v>46324.041666666664</v>
       </c>
       <c r="L71" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="72" spans="1:12">
@@ -3642,28 +3645,28 @@
         <v>13</v>
       </c>
       <c r="C72" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="D72" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F72" t="s">
-        <v>183</v>
+        <v>23</v>
       </c>
       <c r="I72" t="s">
         <v>18</v>
       </c>
       <c r="J72" s="2">
-        <v>46323.622916666667</v>
+        <v>46323.625</v>
       </c>
       <c r="K72" s="2">
-        <v>46324.875</v>
+        <v>46327.541666666664</v>
       </c>
       <c r="L72" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="73" spans="1:12">
@@ -3671,37 +3674,31 @@
         <v>12</v>
       </c>
       <c r="B73" t="s">
-        <v>69</v>
+        <v>13</v>
       </c>
       <c r="C73" t="s">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="D73" t="s">
-        <v>71</v>
-      </c>
-      <c r="E73" s="1">
-        <v>26173</v>
+        <v>182</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>183</v>
       </c>
       <c r="F73" t="s">
-        <v>72</v>
-      </c>
-      <c r="G73" t="s">
-        <v>73</v>
-      </c>
-      <c r="H73" t="s">
-        <v>73</v>
+        <v>23</v>
       </c>
       <c r="I73" t="s">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="J73" s="2">
         <v>46323.625</v>
       </c>
       <c r="K73" s="2">
-        <v>46324.041666666664</v>
+        <v>46327.541666666664</v>
       </c>
       <c r="L73" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="74" spans="1:12">
@@ -3709,10 +3706,10 @@
         <v>12</v>
       </c>
       <c r="B74" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="C74" t="s">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="D74" t="s">
         <v>184</v>
@@ -3727,13 +3724,13 @@
         <v>18</v>
       </c>
       <c r="J74" s="2">
-        <v>46323.625</v>
+        <v>46323.661111111112</v>
       </c>
       <c r="K74" s="2">
-        <v>46327.541666666664</v>
+        <v>46327.202777777777</v>
       </c>
       <c r="L74" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="75" spans="1:12">
@@ -3741,10 +3738,10 @@
         <v>12</v>
       </c>
       <c r="B75" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="C75" t="s">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="D75" t="s">
         <v>184</v>
@@ -3759,13 +3756,13 @@
         <v>18</v>
       </c>
       <c r="J75" s="2">
-        <v>46323.625</v>
+        <v>46323.661111111112</v>
       </c>
       <c r="K75" s="2">
-        <v>46327.541666666664</v>
+        <v>46327.202777777777</v>
       </c>
       <c r="L75" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="76" spans="1:12">
@@ -3773,31 +3770,34 @@
         <v>12</v>
       </c>
       <c r="B76" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="C76" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="D76" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="F76" t="s">
         <v>23</v>
       </c>
+      <c r="G76" t="s">
+        <v>17</v>
+      </c>
       <c r="I76" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J76" s="2">
-        <v>46323.661111111112</v>
+        <v>46323.791666666664</v>
       </c>
       <c r="K76" s="2">
-        <v>46327.202777777777</v>
+        <v>46324.75</v>
       </c>
       <c r="L76" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
     <row r="77" spans="1:12">
@@ -3805,10 +3805,7 @@
         <v>12</v>
       </c>
       <c r="B77" t="s">
-        <v>36</v>
-      </c>
-      <c r="C77" t="s">
-        <v>55</v>
+        <v>121</v>
       </c>
       <c r="D77" t="s">
         <v>186</v>
@@ -3817,147 +3814,147 @@
         <v>187</v>
       </c>
       <c r="F77" t="s">
-        <v>23</v>
+        <v>125</v>
       </c>
       <c r="I77" t="s">
         <v>18</v>
       </c>
       <c r="J77" s="2">
-        <v>46323.661111111112</v>
+        <v>46324</v>
       </c>
       <c r="K77" s="2">
-        <v>46327.202777777777</v>
+        <v>46326</v>
       </c>
       <c r="L77" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="78" spans="1:12">
       <c r="A78" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B78" t="s">
-        <v>75</v>
+        <v>28</v>
       </c>
       <c r="C78" t="s">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="D78" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="F78" t="s">
-        <v>23</v>
-      </c>
-      <c r="G78" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="I78" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J78" s="2">
-        <v>46323.791666666664</v>
+        <v>46325.003472222219</v>
       </c>
       <c r="K78" s="2">
-        <v>46324.75</v>
+        <v>46325.878472222219</v>
       </c>
       <c r="L78" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
     </row>
     <row r="79" spans="1:12">
       <c r="A79" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B79" t="s">
-        <v>121</v>
+        <v>61</v>
+      </c>
+      <c r="C79" t="s">
+        <v>79</v>
       </c>
       <c r="D79" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F79" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="I79" t="s">
         <v>18</v>
       </c>
       <c r="J79" s="2">
-        <v>46324</v>
+        <v>46325.056944444441</v>
       </c>
       <c r="K79" s="2">
-        <v>46326</v>
+        <v>46326.098611111112</v>
       </c>
       <c r="L79" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="80" spans="1:12">
       <c r="A80" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B80" t="s">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="C80" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="D80" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F80" t="s">
-        <v>31</v>
+        <v>23</v>
+      </c>
+      <c r="G80" t="s">
+        <v>17</v>
       </c>
       <c r="I80" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J80" s="2">
-        <v>46325.003472222219</v>
+        <v>46325.25</v>
       </c>
       <c r="K80" s="2">
-        <v>46325.878472222219</v>
+        <v>46325.75</v>
       </c>
       <c r="L80" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
     <row r="81" spans="1:12">
       <c r="A81" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B81" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C81" t="s">
-        <v>83</v>
+        <v>45</v>
       </c>
       <c r="D81" t="s">
-        <v>192</v>
-      </c>
-      <c r="E81" s="1" t="s">
-        <v>193</v>
+        <v>133</v>
       </c>
       <c r="F81" t="s">
-        <v>86</v>
+        <v>48</v>
       </c>
       <c r="I81" t="s">
         <v>18</v>
       </c>
       <c r="J81" s="2">
-        <v>46325.056944444441</v>
+        <v>46325.333333333336</v>
       </c>
       <c r="K81" s="2">
-        <v>46326.098611111112</v>
+        <v>46325.833333333336</v>
       </c>
       <c r="L81" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="82" spans="1:12">
@@ -3965,34 +3962,37 @@
         <v>12</v>
       </c>
       <c r="B82" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C82" t="s">
-        <v>21</v>
+        <v>97</v>
       </c>
       <c r="D82" t="s">
-        <v>194</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>195</v>
+        <v>98</v>
+      </c>
+      <c r="E82" s="1">
+        <v>26172</v>
       </c>
       <c r="F82" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="G82" t="s">
-        <v>17</v>
+        <v>69</v>
+      </c>
+      <c r="H82" t="s">
+        <v>69</v>
       </c>
       <c r="I82" t="s">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="J82" s="2">
-        <v>46325.25</v>
+        <v>46325.625</v>
       </c>
       <c r="K82" s="2">
-        <v>46325.75</v>
+        <v>46326.041666666664</v>
       </c>
       <c r="L82" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
     </row>
     <row r="83" spans="1:12">
@@ -4000,25 +4000,31 @@
         <v>12</v>
       </c>
       <c r="B83" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="C83" t="s">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="D83" t="s">
-        <v>133</v>
+        <v>192</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>193</v>
       </c>
       <c r="F83" t="s">
-        <v>53</v>
+        <v>23</v>
+      </c>
+      <c r="G83" t="s">
+        <v>17</v>
       </c>
       <c r="I83" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J83" s="2">
-        <v>46325.333333333336</v>
+        <v>46325.791666666664</v>
       </c>
       <c r="K83" s="2">
-        <v>46325.833333333336</v>
+        <v>46326.75</v>
       </c>
       <c r="L83" t="s">
         <v>26</v>
@@ -4026,37 +4032,34 @@
     </row>
     <row r="84" spans="1:12">
       <c r="A84" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B84" t="s">
-        <v>69</v>
+        <v>28</v>
       </c>
       <c r="C84" t="s">
-        <v>100</v>
+        <v>32</v>
       </c>
       <c r="D84" t="s">
-        <v>101</v>
-      </c>
-      <c r="E84" s="1">
-        <v>26172</v>
+        <v>194</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>195</v>
       </c>
       <c r="F84" t="s">
-        <v>72</v>
-      </c>
-      <c r="G84" t="s">
-        <v>73</v>
-      </c>
-      <c r="H84" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="I84" t="s">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="J84" s="2">
-        <v>46325.625</v>
+        <v>46326.166666666664</v>
       </c>
       <c r="K84" s="2">
-        <v>46326.041666666664</v>
+        <v>46328.125</v>
+      </c>
+      <c r="L84" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="85" spans="1:12">
@@ -4064,16 +4067,16 @@
         <v>12</v>
       </c>
       <c r="B85" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C85" t="s">
         <v>21</v>
       </c>
       <c r="D85" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F85" t="s">
         <v>23</v>
@@ -4085,7 +4088,7 @@
         <v>25</v>
       </c>
       <c r="J85" s="2">
-        <v>46325.791666666664</v>
+        <v>46326.25</v>
       </c>
       <c r="K85" s="2">
         <v>46326.75</v>
@@ -4096,34 +4099,31 @@
     </row>
     <row r="86" spans="1:12">
       <c r="A86" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B86" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="C86" t="s">
-        <v>32</v>
+        <v>92</v>
       </c>
       <c r="D86" t="s">
-        <v>196</v>
-      </c>
-      <c r="E86" s="1" t="s">
-        <v>197</v>
+        <v>93</v>
       </c>
       <c r="F86" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="I86" t="s">
         <v>18</v>
       </c>
       <c r="J86" s="2">
-        <v>46326.166666666664</v>
+        <v>46326.416666666664</v>
       </c>
       <c r="K86" s="2">
-        <v>46328.125</v>
+        <v>46326.75</v>
       </c>
       <c r="L86" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="87" spans="1:12">
@@ -4131,10 +4131,10 @@
         <v>12</v>
       </c>
       <c r="B87" t="s">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="C87" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="D87" t="s">
         <v>198</v>
@@ -4143,51 +4143,51 @@
         <v>199</v>
       </c>
       <c r="F87" t="s">
-        <v>23</v>
-      </c>
-      <c r="G87" t="s">
-        <v>17</v>
+        <v>181</v>
       </c>
       <c r="I87" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J87" s="2">
-        <v>46326.25</v>
+        <v>46326.833333333336</v>
       </c>
       <c r="K87" s="2">
-        <v>46326.75</v>
+        <v>46329.583333333336</v>
       </c>
       <c r="L87" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
     </row>
     <row r="88" spans="1:12">
       <c r="A88" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B88" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="C88" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="D88" t="s">
-        <v>96</v>
+        <v>200</v>
+      </c>
+      <c r="E88" s="1">
+        <v>69</v>
       </c>
       <c r="F88" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="I88" t="s">
         <v>18</v>
       </c>
       <c r="J88" s="2">
-        <v>46326.416666666664</v>
+        <v>46327.166666666664</v>
       </c>
       <c r="K88" s="2">
-        <v>46326.75</v>
+        <v>46328.541666666664</v>
       </c>
       <c r="L88" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="89" spans="1:12">
@@ -4195,31 +4195,34 @@
         <v>12</v>
       </c>
       <c r="B89" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="C89" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="D89" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F89" t="s">
-        <v>183</v>
+        <v>116</v>
+      </c>
+      <c r="G89" t="s">
+        <v>17</v>
       </c>
       <c r="I89" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J89" s="2">
-        <v>46326.833333333336</v>
+        <v>46327.25</v>
       </c>
       <c r="K89" s="2">
-        <v>46329.583333333336</v>
+        <v>46327.75</v>
       </c>
       <c r="L89" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
     <row r="90" spans="1:12">
@@ -4227,31 +4230,25 @@
         <v>27</v>
       </c>
       <c r="B90" t="s">
-        <v>40</v>
-      </c>
-      <c r="C90" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D90" t="s">
-        <v>202</v>
-      </c>
-      <c r="E90" s="1" t="s">
         <v>203</v>
       </c>
       <c r="F90" t="s">
-        <v>68</v>
+        <v>120</v>
       </c>
       <c r="I90" t="s">
         <v>18</v>
       </c>
       <c r="J90" s="2">
-        <v>46327.166666666664</v>
+        <v>46327.708333333336</v>
       </c>
       <c r="K90" s="2">
-        <v>46328.541666666664</v>
+        <v>46328.833333333336</v>
       </c>
       <c r="L90" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="91" spans="1:12">
@@ -4259,19 +4256,19 @@
         <v>12</v>
       </c>
       <c r="B91" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="C91" t="s">
         <v>21</v>
       </c>
       <c r="D91" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="F91" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G91" t="s">
         <v>17</v>
@@ -4280,10 +4277,10 @@
         <v>25</v>
       </c>
       <c r="J91" s="2">
-        <v>46327.25</v>
+        <v>46327.791666666664</v>
       </c>
       <c r="K91" s="2">
-        <v>46327.75</v>
+        <v>46328.75</v>
       </c>
       <c r="L91" t="s">
         <v>26</v>
@@ -4291,28 +4288,34 @@
     </row>
     <row r="92" spans="1:12">
       <c r="A92" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B92" t="s">
-        <v>40</v>
+        <v>35</v>
+      </c>
+      <c r="C92" t="s">
+        <v>36</v>
       </c>
       <c r="D92" t="s">
-        <v>206</v>
+        <v>204</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>205</v>
       </c>
       <c r="F92" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="I92" t="s">
         <v>18</v>
       </c>
       <c r="J92" s="2">
-        <v>46327.708333333336</v>
+        <v>46327.904861111114</v>
       </c>
       <c r="K92" s="2">
-        <v>46328.833333333336</v>
+        <v>46331.196527777778</v>
       </c>
       <c r="L92" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="93" spans="1:12">
@@ -4320,34 +4323,31 @@
         <v>12</v>
       </c>
       <c r="B93" t="s">
-        <v>75</v>
+        <v>121</v>
       </c>
       <c r="C93" t="s">
-        <v>21</v>
+        <v>122</v>
       </c>
       <c r="D93" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="F93" t="s">
-        <v>115</v>
-      </c>
-      <c r="G93" t="s">
-        <v>17</v>
+        <v>125</v>
       </c>
       <c r="I93" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J93" s="2">
-        <v>46327.791666666664</v>
+        <v>46329</v>
       </c>
       <c r="K93" s="2">
-        <v>46328.75</v>
+        <v>46330</v>
       </c>
       <c r="L93" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
     </row>
     <row r="94" spans="1:12">
@@ -4355,89 +4355,86 @@
         <v>12</v>
       </c>
       <c r="B94" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="C94" t="s">
-        <v>37</v>
+        <v>99</v>
       </c>
       <c r="D94" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F94" t="s">
-        <v>23</v>
+        <v>181</v>
       </c>
       <c r="I94" t="s">
         <v>18</v>
       </c>
       <c r="J94" s="2">
-        <v>46327.904861111114</v>
+        <v>46329.333333333336</v>
       </c>
       <c r="K94" s="2">
-        <v>46331.196527777778</v>
+        <v>46332.625</v>
       </c>
       <c r="L94" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="95" spans="1:12">
       <c r="A95" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B95" t="s">
-        <v>13</v>
-      </c>
-      <c r="C95" t="s">
-        <v>102</v>
+        <v>61</v>
       </c>
       <c r="D95" t="s">
-        <v>209</v>
-      </c>
-      <c r="E95" s="1" t="s">
         <v>210</v>
       </c>
       <c r="F95" t="s">
-        <v>183</v>
+        <v>120</v>
       </c>
       <c r="I95" t="s">
         <v>18</v>
       </c>
       <c r="J95" s="2">
-        <v>46329.333333333336</v>
+        <v>46330.083333333336</v>
       </c>
       <c r="K95" s="2">
-        <v>46332.625</v>
+        <v>46331.208333333336</v>
       </c>
       <c r="L95" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="96" spans="1:12">
       <c r="A96" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B96" t="s">
-        <v>40</v>
+        <v>65</v>
+      </c>
+      <c r="C96" t="s">
+        <v>66</v>
       </c>
       <c r="D96" t="s">
-        <v>211</v>
+        <v>67</v>
       </c>
       <c r="F96" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="I96" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="J96" s="2">
-        <v>46330.083333333336</v>
+        <v>46330.625</v>
       </c>
       <c r="K96" s="2">
-        <v>46331.208333333336</v>
+        <v>46331.125</v>
       </c>
       <c r="L96" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="97" spans="1:12">
@@ -4445,31 +4442,31 @@
         <v>12</v>
       </c>
       <c r="B97" t="s">
-        <v>121</v>
+        <v>13</v>
       </c>
       <c r="C97" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="D97" t="s">
+        <v>211</v>
+      </c>
+      <c r="E97" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="E97" s="1" t="s">
-        <v>213</v>
-      </c>
       <c r="F97" t="s">
-        <v>125</v>
+        <v>181</v>
       </c>
       <c r="I97" t="s">
         <v>18</v>
       </c>
       <c r="J97" s="2">
-        <v>46330.208333333336</v>
+        <v>46330.633333333331</v>
       </c>
       <c r="K97" s="2">
-        <v>46333.208333333336</v>
+        <v>46333.925000000003</v>
       </c>
       <c r="L97" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="98" spans="1:12">
@@ -4477,28 +4474,31 @@
         <v>12</v>
       </c>
       <c r="B98" t="s">
-        <v>69</v>
+        <v>13</v>
       </c>
       <c r="C98" t="s">
-        <v>70</v>
+        <v>99</v>
       </c>
       <c r="D98" t="s">
-        <v>71</v>
+        <v>211</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>212</v>
       </c>
       <c r="F98" t="s">
-        <v>72</v>
+        <v>181</v>
       </c>
       <c r="I98" t="s">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="J98" s="2">
-        <v>46330.625</v>
+        <v>46330.633333333331</v>
       </c>
       <c r="K98" s="2">
-        <v>46331.125</v>
+        <v>46333.925000000003</v>
       </c>
       <c r="L98" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="99" spans="1:12">
@@ -4506,92 +4506,92 @@
         <v>12</v>
       </c>
       <c r="B99" t="s">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="C99" t="s">
-        <v>102</v>
+        <v>45</v>
       </c>
       <c r="D99" t="s">
-        <v>214</v>
-      </c>
-      <c r="E99" s="1" t="s">
-        <v>215</v>
+        <v>159</v>
       </c>
       <c r="F99" t="s">
-        <v>183</v>
+        <v>48</v>
       </c>
       <c r="I99" t="s">
         <v>18</v>
       </c>
       <c r="J99" s="2">
-        <v>46330.633333333331</v>
+        <v>46330.704861111109</v>
       </c>
       <c r="K99" s="2">
-        <v>46333.925000000003</v>
+        <v>46331.204861111109</v>
       </c>
       <c r="L99" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="100" spans="1:12">
       <c r="A100" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B100" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="C100" t="s">
-        <v>102</v>
+        <v>32</v>
       </c>
       <c r="D100" t="s">
+        <v>213</v>
+      </c>
+      <c r="E100" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="E100" s="1" t="s">
-        <v>215</v>
-      </c>
       <c r="F100" t="s">
-        <v>183</v>
+        <v>31</v>
       </c>
       <c r="I100" t="s">
         <v>18</v>
       </c>
       <c r="J100" s="2">
-        <v>46330.633333333331</v>
+        <v>46330.75</v>
       </c>
       <c r="K100" s="2">
-        <v>46333.925000000003</v>
+        <v>46332.75</v>
       </c>
       <c r="L100" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="101" spans="1:12">
       <c r="A101" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B101" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="C101" t="s">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="D101" t="s">
-        <v>159</v>
+        <v>215</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>216</v>
       </c>
       <c r="F101" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="I101" t="s">
         <v>18</v>
       </c>
       <c r="J101" s="2">
-        <v>46330.704861111109</v>
+        <v>46331.020833333336</v>
       </c>
       <c r="K101" s="2">
-        <v>46331.204861111109</v>
+        <v>46332.520833333336</v>
       </c>
       <c r="L101" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="102" spans="1:12">
@@ -4602,12 +4602,9 @@
         <v>28</v>
       </c>
       <c r="C102" t="s">
-        <v>32</v>
+        <v>84</v>
       </c>
       <c r="D102" t="s">
-        <v>216</v>
-      </c>
-      <c r="E102" s="1" t="s">
         <v>217</v>
       </c>
       <c r="F102" t="s">
@@ -4617,24 +4614,24 @@
         <v>18</v>
       </c>
       <c r="J102" s="2">
-        <v>46330.75</v>
+        <v>46331.291666666664</v>
       </c>
       <c r="K102" s="2">
-        <v>46332.75</v>
+        <v>46332.166666666664</v>
       </c>
       <c r="L102" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="103" spans="1:12">
       <c r="A103" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B103" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C103" t="s">
-        <v>79</v>
+        <v>36</v>
       </c>
       <c r="D103" t="s">
         <v>218</v>
@@ -4643,176 +4640,185 @@
         <v>219</v>
       </c>
       <c r="F103" t="s">
-        <v>68</v>
+        <v>181</v>
       </c>
       <c r="I103" t="s">
         <v>18</v>
       </c>
       <c r="J103" s="2">
-        <v>46331.020833333336</v>
+        <v>46331.496527777781</v>
       </c>
       <c r="K103" s="2">
-        <v>46332.520833333336</v>
+        <v>46334.746527777781</v>
       </c>
       <c r="L103" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="104" spans="1:12">
       <c r="A104" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B104" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C104" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D104" t="s">
-        <v>220</v>
+        <v>218</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>219</v>
       </c>
       <c r="F104" t="s">
-        <v>31</v>
+        <v>181</v>
       </c>
       <c r="I104" t="s">
         <v>18</v>
       </c>
       <c r="J104" s="2">
-        <v>46331.291666666664</v>
+        <v>46331.496527777781</v>
       </c>
       <c r="K104" s="2">
-        <v>46332.166666666664</v>
+        <v>46334.746527777781</v>
       </c>
       <c r="L104" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="105" spans="1:12">
       <c r="A105" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B105" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="C105" t="s">
-        <v>37</v>
+        <v>149</v>
       </c>
       <c r="D105" t="s">
+        <v>220</v>
+      </c>
+      <c r="E105" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="E105" s="1" t="s">
-        <v>222</v>
-      </c>
       <c r="F105" t="s">
-        <v>183</v>
+        <v>82</v>
       </c>
       <c r="I105" t="s">
         <v>18</v>
       </c>
       <c r="J105" s="2">
-        <v>46331.496527777781</v>
+        <v>46332.056250000001</v>
       </c>
       <c r="K105" s="2">
-        <v>46334.746527777781</v>
+        <v>46332.597916666666</v>
       </c>
       <c r="L105" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="106" spans="1:12">
       <c r="A106" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B106" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="C106" t="s">
-        <v>37</v>
+        <v>106</v>
       </c>
       <c r="D106" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F106" t="s">
-        <v>183</v>
+        <v>109</v>
       </c>
       <c r="I106" t="s">
         <v>18</v>
       </c>
       <c r="J106" s="2">
-        <v>46331.496527777781</v>
+        <v>46332.083333333336</v>
       </c>
       <c r="K106" s="2">
-        <v>46334.746527777781</v>
+        <v>46333.291666666664</v>
       </c>
       <c r="L106" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="107" spans="1:12">
       <c r="A107" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B107" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="C107" t="s">
-        <v>149</v>
+        <v>21</v>
       </c>
       <c r="D107" t="s">
-        <v>223</v>
-      </c>
-      <c r="E107" s="1" t="s">
         <v>224</v>
       </c>
+      <c r="E107" s="1">
+        <v>10</v>
+      </c>
       <c r="F107" t="s">
-        <v>86</v>
+        <v>58</v>
+      </c>
+      <c r="G107" t="s">
+        <v>17</v>
       </c>
       <c r="I107" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J107" s="2">
-        <v>46332.056250000001</v>
+        <v>46332.25</v>
       </c>
       <c r="K107" s="2">
-        <v>46332.597916666666</v>
+        <v>46332.75</v>
       </c>
       <c r="L107" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
     <row r="108" spans="1:12">
       <c r="A108" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B108" t="s">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="C108" t="s">
-        <v>108</v>
+        <v>21</v>
       </c>
       <c r="D108" t="s">
         <v>225</v>
       </c>
-      <c r="E108" s="1" t="s">
-        <v>226</v>
+      <c r="E108" s="1">
+        <v>1</v>
       </c>
       <c r="F108" t="s">
-        <v>111</v>
+        <v>58</v>
+      </c>
+      <c r="G108" t="s">
+        <v>17</v>
       </c>
       <c r="I108" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J108" s="2">
-        <v>46332.083333333336</v>
+        <v>46332.25</v>
       </c>
       <c r="K108" s="2">
-        <v>46333.291666666664</v>
+        <v>46332.75</v>
       </c>
       <c r="L108" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
     <row r="109" spans="1:12">
@@ -4820,34 +4826,31 @@
         <v>12</v>
       </c>
       <c r="B109" t="s">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="C109" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D109" t="s">
+        <v>226</v>
+      </c>
+      <c r="E109" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="E109" s="1">
-        <v>10</v>
-      </c>
       <c r="F109" t="s">
-        <v>62</v>
-      </c>
-      <c r="G109" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I109" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J109" s="2">
         <v>46332.25</v>
       </c>
       <c r="K109" s="2">
-        <v>46332.75</v>
+        <v>46336.041666666664</v>
       </c>
       <c r="L109" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
     </row>
     <row r="110" spans="1:12">
@@ -4855,34 +4858,31 @@
         <v>12</v>
       </c>
       <c r="B110" t="s">
-        <v>75</v>
+        <v>13</v>
       </c>
       <c r="C110" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D110" t="s">
-        <v>228</v>
-      </c>
-      <c r="E110" s="1">
-        <v>1</v>
+        <v>226</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>227</v>
       </c>
       <c r="F110" t="s">
-        <v>62</v>
-      </c>
-      <c r="G110" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I110" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J110" s="2">
         <v>46332.25</v>
       </c>
       <c r="K110" s="2">
-        <v>46332.75</v>
+        <v>46336.041666666664</v>
       </c>
       <c r="L110" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
     </row>
     <row r="111" spans="1:12">
@@ -4890,31 +4890,28 @@
         <v>12</v>
       </c>
       <c r="B111" t="s">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="C111" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="D111" t="s">
-        <v>229</v>
-      </c>
-      <c r="E111" s="1" t="s">
-        <v>230</v>
+        <v>87</v>
       </c>
       <c r="F111" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="I111" t="s">
         <v>18</v>
       </c>
       <c r="J111" s="2">
-        <v>46332.25</v>
+        <v>46332.291666666664</v>
       </c>
       <c r="K111" s="2">
-        <v>46336.041666666664</v>
+        <v>46332.791666666664</v>
       </c>
       <c r="L111" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="112" spans="1:12">
@@ -4922,86 +4919,28 @@
         <v>12</v>
       </c>
       <c r="B112" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="C112" t="s">
-        <v>14</v>
+        <v>97</v>
       </c>
       <c r="D112" t="s">
-        <v>229</v>
-      </c>
-      <c r="E112" s="1" t="s">
-        <v>230</v>
+        <v>98</v>
       </c>
       <c r="F112" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="I112" t="s">
         <v>18</v>
       </c>
       <c r="J112" s="2">
-        <v>46332.25</v>
+        <v>46332.541666666664</v>
       </c>
       <c r="K112" s="2">
-        <v>46336.041666666664</v>
+        <v>46333.041666666664</v>
       </c>
       <c r="L112" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="113" spans="1:12">
-      <c r="A113" t="s">
-        <v>12</v>
-      </c>
-      <c r="B113" t="s">
-        <v>49</v>
-      </c>
-      <c r="C113" t="s">
-        <v>50</v>
-      </c>
-      <c r="D113" t="s">
-        <v>90</v>
-      </c>
-      <c r="F113" t="s">
-        <v>53</v>
-      </c>
-      <c r="I113" t="s">
-        <v>18</v>
-      </c>
-      <c r="J113" s="2">
-        <v>46332.291666666664</v>
-      </c>
-      <c r="K113" s="2">
-        <v>46332.791666666664</v>
-      </c>
-      <c r="L113" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="114" spans="1:12">
-      <c r="A114" t="s">
-        <v>12</v>
-      </c>
-      <c r="B114" t="s">
-        <v>69</v>
-      </c>
-      <c r="C114" t="s">
-        <v>100</v>
-      </c>
-      <c r="D114" t="s">
-        <v>101</v>
-      </c>
-      <c r="F114" t="s">
-        <v>72</v>
-      </c>
-      <c r="I114" t="s">
-        <v>18</v>
-      </c>
-      <c r="J114" s="2">
-        <v>46332.541666666664</v>
-      </c>
-      <c r="K114" s="2">
-        <v>46333.041666666664</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -5013,12 +4952,29 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<scriptIds xmlns="http://schemas.microsoft.com/office/extensibility/maker/v1.0" id="script-ids-node-id">
+  <scriptId id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFlYmU2eGFOY1prSzQ4ZzMwOVNrOE5z"/>
+  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJYSQ36AWKC2TNDYVMQR2CLHJFKM:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQVNodndMS0ZxYlI0cXlFZENXZEpWTUFiamQ5UnJqRGdfNHFKblptMGRDaTk4"/>
+  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFjcU1YSmx2clY5eXMzT2hWMXFuc2ZZ"/>
+</scriptIds>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A69D21F4021FF043AD25F7555C34E75C" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ada5bbc6177f3d5462a6af737539cf89">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="169fe4b0-aa95-4062-90d3-821d069df163" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ce4529c032f5bb0135a70d700e81f25b" ns2:_="">
     <xsd:import namespace="169fe4b0-aa95-4062-90d3-821d069df163"/>
@@ -5156,35 +5112,18 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{090E8699-A26C-4C66-9B6D-70C00CB2CACE}"/>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<scriptIds xmlns="http://schemas.microsoft.com/office/extensibility/maker/v1.0" id="script-ids-node-id">
-  <scriptId id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFlYmU2eGFOY1prSzQ4ZzMwOVNrOE5z"/>
-  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJYSQ36AWKC2TNDYVMQR2CLHJFKM:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQVNodndMS0ZxYlI0cXlFZENXZEpWTUFiamQ5UnJqRGdfNHFKblptMGRDaTk4"/>
-  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFjcU1YSmx2clY5eXMzT2hWMXFuc2ZZ"/>
-</scriptIds>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF03C61-A585-446F-A57D-D94F9FA6CAC8}"/>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF8193A-09E0-4717-9CA6-EF5C70C0F2A4}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D94EB81F-BDF3-4640-AE12-B1EC3B704FEB}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{090E8699-A26C-4C66-9B6D-70C00CB2CACE}"/>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF03C61-A585-446F-A57D-D94F9FA6CAC8}"/>
 </file>
--- a/data/vessels/2026-10-12.xlsx
+++ b/data/vessels/2026-10-12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://portoftacoma.sharepoint.com/sites/dnateam-Technical/Shared Documents/Technical/External Dashboards/Vessel Schedule/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="419729" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0A76BFF8-5344-4CF6-8E0D-4EC2E0AC78D7}"/>
+  <xr:revisionPtr revIDLastSave="420454" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46A461CA-8172-468E-9801-8E1B25ACD4CF}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6E7AA7D4-05A2-4831-A105-C5B1AC660A61}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="948" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="963" uniqueCount="229">
   <si>
     <t>Harbor</t>
   </si>
@@ -158,21 +158,33 @@
     <t>088W</t>
   </si>
   <si>
+    <t>T18</t>
+  </si>
+  <si>
+    <t>SM SEOUL</t>
+  </si>
+  <si>
+    <t>2607E/2607W</t>
+  </si>
+  <si>
+    <t>SM Line</t>
+  </si>
+  <si>
+    <t>In transit</t>
+  </si>
+  <si>
+    <t>MSC PINA</t>
+  </si>
+  <si>
+    <t>UK639R</t>
+  </si>
+  <si>
     <t>MSC BOSTON</t>
   </si>
   <si>
     <t>MC641R</t>
   </si>
   <si>
-    <t>MSC PINA</t>
-  </si>
-  <si>
-    <t>UK639R</t>
-  </si>
-  <si>
-    <t>In transit</t>
-  </si>
-  <si>
     <t>WST</t>
   </si>
   <si>
@@ -203,7 +215,7 @@
     <t>HMM</t>
   </si>
   <si>
-    <t>Waiting 1.1 days</t>
+    <t>Waiting 1.3 days</t>
   </si>
   <si>
     <t>EB1</t>
@@ -224,7 +236,61 @@
     <t>158A</t>
   </si>
   <si>
-    <t>T18</t>
+    <t>TOTE</t>
+  </si>
+  <si>
+    <t>Tote - AK1</t>
+  </si>
+  <si>
+    <t>MIDNIGHT SUN</t>
+  </si>
+  <si>
+    <t>Tote</t>
+  </si>
+  <si>
+    <t>Tote Maritime Alaska Inc</t>
+  </si>
+  <si>
+    <t>Multipurpose</t>
+  </si>
+  <si>
+    <t>Blair</t>
+  </si>
+  <si>
+    <t>LIBERTY PRIDE</t>
+  </si>
+  <si>
+    <t>Liberty</t>
+  </si>
+  <si>
+    <t>Pacific Terminals</t>
+  </si>
+  <si>
+    <t>EB Service 2</t>
+  </si>
+  <si>
+    <t>SUVA CHIEF</t>
+  </si>
+  <si>
+    <t>007E/008W</t>
+  </si>
+  <si>
+    <t>Swire</t>
+  </si>
+  <si>
+    <t>Talon Marine Services LLC</t>
+  </si>
+  <si>
+    <t>Oceania</t>
+  </si>
+  <si>
+    <t>LONG BEACH EXPRESS</t>
+  </si>
+  <si>
+    <t>636N/642S</t>
+  </si>
+  <si>
+    <t>Hapag-Lloyd</t>
   </si>
   <si>
     <t>CMA CGM BYBLOS</t>
@@ -236,63 +302,6 @@
     <t>CMA CGM</t>
   </si>
   <si>
-    <t>TOTE</t>
-  </si>
-  <si>
-    <t>Tote - AK1</t>
-  </si>
-  <si>
-    <t>MIDNIGHT SUN</t>
-  </si>
-  <si>
-    <t>Tote</t>
-  </si>
-  <si>
-    <t>Tote Maritime Alaska Inc</t>
-  </si>
-  <si>
-    <t>Multipurpose</t>
-  </si>
-  <si>
-    <t>Blair</t>
-  </si>
-  <si>
-    <t>LIBERTY PRIDE</t>
-  </si>
-  <si>
-    <t>Liberty</t>
-  </si>
-  <si>
-    <t>Pacific Terminals</t>
-  </si>
-  <si>
-    <t>Oceania</t>
-  </si>
-  <si>
-    <t>LONG BEACH EXPRESS</t>
-  </si>
-  <si>
-    <t>636N/642S</t>
-  </si>
-  <si>
-    <t>Hapag-Lloyd</t>
-  </si>
-  <si>
-    <t>EB Service 2</t>
-  </si>
-  <si>
-    <t>SUVA CHIEF</t>
-  </si>
-  <si>
-    <t>007E/008W</t>
-  </si>
-  <si>
-    <t>Swire</t>
-  </si>
-  <si>
-    <t>Talon Marine Services LLC</t>
-  </si>
-  <si>
     <t>CLX</t>
   </si>
   <si>
@@ -374,36 +383,30 @@
     <t>COSCO SHIPPING LINES</t>
   </si>
   <si>
+    <t>MODERN LINK</t>
+  </si>
+  <si>
+    <t>THEMISA</t>
+  </si>
+  <si>
+    <t>ED615</t>
+  </si>
+  <si>
+    <t>Wallenius</t>
+  </si>
+  <si>
     <t>SALVIA ACE</t>
   </si>
   <si>
     <t>177A</t>
   </si>
   <si>
-    <t>MODERN LINK</t>
-  </si>
-  <si>
-    <t>THEMISA</t>
-  </si>
-  <si>
-    <t>ED615</t>
-  </si>
-  <si>
-    <t>Wallenius</t>
+    <t>SM QINGDAO</t>
   </si>
   <si>
     <t>ONE OWL</t>
   </si>
   <si>
-    <t>SM QINGDAO</t>
-  </si>
-  <si>
-    <t>2607E/2607W</t>
-  </si>
-  <si>
-    <t>SM Line</t>
-  </si>
-  <si>
     <t>PCT</t>
   </si>
   <si>
@@ -440,24 +443,24 @@
     <t>UK640R</t>
   </si>
   <si>
+    <t>THEMIS LEADER</t>
+  </si>
+  <si>
+    <t>ARC ENDEAVOR</t>
+  </si>
+  <si>
+    <t>A6180</t>
+  </si>
+  <si>
+    <t>Ports America Group/Pct</t>
+  </si>
+  <si>
     <t>MATSON ANCHORAGE</t>
   </si>
   <si>
     <t>643S</t>
   </si>
   <si>
-    <t>THEMIS LEADER</t>
-  </si>
-  <si>
-    <t>ARC ENDEAVOR</t>
-  </si>
-  <si>
-    <t>A6180</t>
-  </si>
-  <si>
-    <t>Ports America Group/Pct</t>
-  </si>
-  <si>
     <t>VIENNA EXPRESS</t>
   </si>
   <si>
@@ -506,18 +509,18 @@
     <t>POLARIS MILA</t>
   </si>
   <si>
+    <t>OOCL SAN FRANCISCO</t>
+  </si>
+  <si>
+    <t>199E/199W</t>
+  </si>
+  <si>
     <t>MAUNAWILI</t>
   </si>
   <si>
     <t>642S</t>
   </si>
   <si>
-    <t>OOCL SAN FRANCISCO</t>
-  </si>
-  <si>
-    <t>199E</t>
-  </si>
-  <si>
     <t>RJ PFEIFFER</t>
   </si>
   <si>
@@ -533,6 +536,9 @@
     <t>ED616</t>
   </si>
   <si>
+    <t>SM PORTLAND</t>
+  </si>
+  <si>
     <t>EVER SALUTE</t>
   </si>
   <si>
@@ -569,7 +575,10 @@
     <t>LIBERTY PASSION</t>
   </si>
   <si>
-    <t>SM PORTLAND</t>
+    <t>FRANKFURT EXPRESS</t>
+  </si>
+  <si>
+    <t>640E/643W</t>
   </si>
   <si>
     <t>PATARA</t>
@@ -578,67 +587,61 @@
     <t>005A</t>
   </si>
   <si>
-    <t>FRANKFURT EXPRESS</t>
-  </si>
-  <si>
-    <t>640E</t>
+    <t>ONE SYNERGY</t>
+  </si>
+  <si>
+    <t>JOYN0002E</t>
+  </si>
+  <si>
+    <t>ONE DURBAN</t>
+  </si>
+  <si>
+    <t>PN32639W</t>
+  </si>
+  <si>
+    <t>EVER MODE</t>
+  </si>
+  <si>
+    <t>1473-010E</t>
+  </si>
+  <si>
+    <t>MSC NITYA B</t>
+  </si>
+  <si>
+    <t>MC637A</t>
+  </si>
+  <si>
+    <t>NADI CHIEF</t>
+  </si>
+  <si>
+    <t>14E</t>
+  </si>
+  <si>
+    <t>SWIFT ACE</t>
+  </si>
+  <si>
+    <t>152A</t>
+  </si>
+  <si>
+    <t>MSC SOLA</t>
+  </si>
+  <si>
+    <t>UK639A</t>
+  </si>
+  <si>
+    <t>LAVENDER ACE</t>
+  </si>
+  <si>
+    <t>123A</t>
+  </si>
+  <si>
+    <t>HYUNDAI FORWARD</t>
+  </si>
+  <si>
+    <t>HHFW0172E</t>
   </si>
   <si>
     <t>Not Specified</t>
-  </si>
-  <si>
-    <t>ONE SYNERGY</t>
-  </si>
-  <si>
-    <t>JOYN0002E</t>
-  </si>
-  <si>
-    <t>ONE DURBAN</t>
-  </si>
-  <si>
-    <t>PN32639W</t>
-  </si>
-  <si>
-    <t>EVER MODE</t>
-  </si>
-  <si>
-    <t>1473-010E</t>
-  </si>
-  <si>
-    <t>MSC NITYA B</t>
-  </si>
-  <si>
-    <t>MC637A</t>
-  </si>
-  <si>
-    <t>NADI CHIEF</t>
-  </si>
-  <si>
-    <t>14E</t>
-  </si>
-  <si>
-    <t>SWIFT ACE</t>
-  </si>
-  <si>
-    <t>152A</t>
-  </si>
-  <si>
-    <t>MSC SOLA</t>
-  </si>
-  <si>
-    <t>UK639A</t>
-  </si>
-  <si>
-    <t>LAVENDER ACE</t>
-  </si>
-  <si>
-    <t>123A</t>
-  </si>
-  <si>
-    <t>HYUNDAI FORWARD</t>
-  </si>
-  <si>
-    <t>HHFW0172E</t>
   </si>
   <si>
     <t>CYPRESS</t>
@@ -795,10 +798,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}" name="Table1" displayName="Table1" ref="A1:L112" totalsRowShown="0">
-  <autoFilter ref="A1:L112" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L112">
-    <sortCondition ref="J2:J112"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}" name="Table1" displayName="Table1" ref="A1:L113" totalsRowShown="0">
+  <autoFilter ref="A1:L113" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L113">
+    <sortCondition ref="J2:J113"/>
   </sortState>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{3ED8A004-BAC7-4959-9663-633E38656002}" name="Harbor"/>
@@ -1135,7 +1138,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9E2A47A-528B-46DE-AE1C-82EC550E6AFE}">
-  <dimension ref="A1:L112"/>
+  <dimension ref="A1:L113"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="10.7109375" customWidth="1"/>
@@ -1216,7 +1219,7 @@
         <v>46303.25</v>
       </c>
       <c r="K2" s="2">
-        <v>46308.166666666664</v>
+        <v>46308.541666666664</v>
       </c>
       <c r="L2" t="s">
         <v>19</v>
@@ -1251,7 +1254,7 @@
         <v>46303.25</v>
       </c>
       <c r="K3" s="2">
-        <v>46308.166666666664</v>
+        <v>46308.541666666664</v>
       </c>
       <c r="L3" t="s">
         <v>19</v>
@@ -1356,7 +1359,7 @@
         <v>46305.208333333336</v>
       </c>
       <c r="K6" s="2">
-        <v>46308.166666666664</v>
+        <v>46308.208333333336</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
@@ -1388,10 +1391,10 @@
         <v>18</v>
       </c>
       <c r="J7" s="2">
-        <v>46306.291666666664</v>
+        <v>46306.208333333336</v>
       </c>
       <c r="K7" s="2">
-        <v>46308.166666666664</v>
+        <v>46308.145833333336</v>
       </c>
       <c r="L7" t="s">
         <v>19</v>
@@ -1426,7 +1429,7 @@
         <v>46306.625</v>
       </c>
       <c r="K8" s="2">
-        <v>46308.75</v>
+        <v>46309.166666666664</v>
       </c>
       <c r="L8" t="s">
         <v>19</v>
@@ -1437,19 +1440,16 @@
         <v>27</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F9" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G9" t="s">
         <v>17</v>
@@ -1458,13 +1458,13 @@
         <v>18</v>
       </c>
       <c r="J9" s="2">
-        <v>46308.291666666664</v>
+        <v>46307.895833333336</v>
       </c>
       <c r="K9" s="2">
-        <v>46309.75</v>
+        <v>46308.75</v>
       </c>
       <c r="L9" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -1478,10 +1478,10 @@
         <v>32</v>
       </c>
       <c r="D10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F10" t="s">
         <v>31</v>
@@ -1504,13 +1504,13 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B11" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="D11" t="s">
         <v>46</v>
@@ -1519,25 +1519,22 @@
         <v>47</v>
       </c>
       <c r="F11" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="G11" t="s">
-        <v>48</v>
-      </c>
-      <c r="H11" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="I11" t="s">
         <v>18</v>
       </c>
       <c r="J11" s="2">
-        <v>46309.104166666664</v>
+        <v>46308.333333333336</v>
       </c>
       <c r="K11" s="2">
-        <v>46309.916666666664</v>
+        <v>46309.75</v>
       </c>
       <c r="L11" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -1545,34 +1542,37 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="C12" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" t="s">
         <v>50</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="F12" t="s">
         <v>52</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
+        <v>52</v>
+      </c>
+      <c r="H12" t="s">
         <v>53</v>
       </c>
-      <c r="G12" t="s">
-        <v>17</v>
-      </c>
       <c r="I12" t="s">
         <v>18</v>
       </c>
       <c r="J12" s="2">
-        <v>46309.208333333336</v>
+        <v>46308.583333333336</v>
       </c>
       <c r="K12" s="2">
-        <v>46310.75</v>
+        <v>46309.916666666664</v>
       </c>
       <c r="L12" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -1580,34 +1580,34 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" t="s">
+        <v>54</v>
+      </c>
+      <c r="D13" t="s">
         <v>55</v>
       </c>
-      <c r="C13" t="s">
-        <v>21</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="E13" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="F13" t="s">
         <v>57</v>
-      </c>
-      <c r="F13" t="s">
-        <v>58</v>
       </c>
       <c r="G13" t="s">
         <v>17</v>
       </c>
       <c r="I13" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J13" s="2">
-        <v>46309.25</v>
+        <v>46309.208333333336</v>
       </c>
       <c r="K13" s="2">
-        <v>46309.708333333336</v>
+        <v>46310.75</v>
       </c>
       <c r="L13" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -1615,19 +1615,19 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C14" t="s">
         <v>21</v>
       </c>
       <c r="D14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F14" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="G14" t="s">
         <v>17</v>
@@ -1636,10 +1636,10 @@
         <v>25</v>
       </c>
       <c r="J14" s="2">
-        <v>46309.541666666664</v>
+        <v>46309.25</v>
       </c>
       <c r="K14" s="2">
-        <v>46310.041666666664</v>
+        <v>46309.708333333336</v>
       </c>
       <c r="L14" t="s">
         <v>26</v>
@@ -1647,34 +1647,34 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C15" t="s">
         <v>21</v>
       </c>
       <c r="D15" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F15" t="s">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="G15" t="s">
         <v>17</v>
       </c>
       <c r="I15" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J15" s="2">
-        <v>46309.625</v>
+        <v>46309.541666666664</v>
       </c>
       <c r="K15" s="2">
-        <v>46311.75</v>
+        <v>46310.041666666664</v>
       </c>
       <c r="L15" t="s">
         <v>26</v>
@@ -1729,13 +1729,13 @@
         <v>21</v>
       </c>
       <c r="D17" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F17" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G17" t="s">
         <v>17</v>
@@ -1758,7 +1758,7 @@
         <v>12</v>
       </c>
       <c r="B18" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C18" t="s">
         <v>21</v>
@@ -1796,7 +1796,7 @@
         <v>27</v>
       </c>
       <c r="B19" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="C19" t="s">
         <v>75</v>
@@ -1811,7 +1811,7 @@
         <v>78</v>
       </c>
       <c r="G19" t="s">
-        <v>17</v>
+        <v>79</v>
       </c>
       <c r="I19" t="s">
         <v>18</v>
@@ -1820,7 +1820,7 @@
         <v>46310.25</v>
       </c>
       <c r="K19" s="2">
-        <v>46311.166666666664</v>
+        <v>46311.708333333336</v>
       </c>
       <c r="L19" t="s">
         <v>43</v>
@@ -1831,22 +1831,22 @@
         <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="C20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D20" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F20" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G20" t="s">
-        <v>83</v>
+        <v>17</v>
       </c>
       <c r="I20" t="s">
         <v>18</v>
@@ -1855,7 +1855,7 @@
         <v>46310.25</v>
       </c>
       <c r="K20" s="2">
-        <v>46311.708333333336</v>
+        <v>46311.166666666664</v>
       </c>
       <c r="L20" t="s">
         <v>43</v>
@@ -1866,19 +1866,19 @@
         <v>27</v>
       </c>
       <c r="B21" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C21" t="s">
+        <v>21</v>
+      </c>
+      <c r="D21" t="s">
         <v>84</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="F21" t="s">
         <v>86</v>
-      </c>
-      <c r="F21" t="s">
-        <v>31</v>
       </c>
       <c r="G21" t="s">
         <v>17</v>
@@ -1887,51 +1887,48 @@
         <v>18</v>
       </c>
       <c r="J21" s="2">
-        <v>46310.291666666664</v>
+        <v>46310.625</v>
       </c>
       <c r="K21" s="2">
-        <v>46311.166666666664</v>
+        <v>46312.708333333336</v>
       </c>
       <c r="L21" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22" spans="1:12">
       <c r="A22" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C22" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="D22" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>47</v>
+        <v>85</v>
       </c>
       <c r="F22" t="s">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="G22" t="s">
-        <v>48</v>
-      </c>
-      <c r="H22" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="I22" t="s">
         <v>18</v>
       </c>
       <c r="J22" s="2">
-        <v>46311.104166666664</v>
+        <v>46310.625</v>
       </c>
       <c r="K22" s="2">
-        <v>46311.916666666664</v>
+        <v>46312.708333333336</v>
       </c>
       <c r="L22" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -1939,34 +1936,31 @@
         <v>27</v>
       </c>
       <c r="B23" t="s">
-        <v>61</v>
+        <v>28</v>
       </c>
       <c r="C23" t="s">
+        <v>87</v>
+      </c>
+      <c r="D23" t="s">
         <v>88</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="E23" s="1" t="s">
-        <v>90</v>
-      </c>
       <c r="F23" t="s">
-        <v>91</v>
+        <v>31</v>
       </c>
       <c r="G23" t="s">
-        <v>24</v>
-      </c>
-      <c r="H23" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="I23" t="s">
         <v>18</v>
       </c>
       <c r="J23" s="2">
-        <v>46311.25</v>
+        <v>46310.708333333336</v>
       </c>
       <c r="K23" s="2">
-        <v>46312.166666666664</v>
+        <v>46311.75</v>
       </c>
       <c r="L23" t="s">
         <v>43</v>
@@ -1977,31 +1971,34 @@
         <v>12</v>
       </c>
       <c r="B24" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C24" t="s">
-        <v>92</v>
+        <v>49</v>
       </c>
       <c r="D24" t="s">
-        <v>93</v>
+        <v>90</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>51</v>
       </c>
       <c r="F24" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G24" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="H24" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I24" t="s">
         <v>18</v>
       </c>
       <c r="J24" s="2">
-        <v>46311.291666666664</v>
+        <v>46311.104166666664</v>
       </c>
       <c r="K24" s="2">
-        <v>46312.125</v>
+        <v>46311.916666666664</v>
       </c>
       <c r="L24" t="s">
         <v>43</v>
@@ -2009,40 +2006,40 @@
     </row>
     <row r="25" spans="1:12">
       <c r="A25" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B25" t="s">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="C25" t="s">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="D25" t="s">
+        <v>92</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F25" t="s">
         <v>94</v>
       </c>
-      <c r="E25" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="F25" t="s">
-        <v>23</v>
-      </c>
       <c r="G25" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="H25" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I25" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="J25" s="2">
-        <v>46311.541666666664</v>
+        <v>46311.25</v>
       </c>
       <c r="K25" s="2">
-        <v>46312.083333333336</v>
+        <v>46312.166666666664</v>
       </c>
       <c r="L25" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -2050,34 +2047,31 @@
         <v>12</v>
       </c>
       <c r="B26" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="C26" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D26" t="s">
-        <v>98</v>
-      </c>
-      <c r="E26" s="1">
-        <v>26164</v>
+        <v>96</v>
       </c>
       <c r="F26" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="G26" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="H26" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="I26" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="J26" s="2">
-        <v>46311.625</v>
+        <v>46311.333333333336</v>
       </c>
       <c r="K26" s="2">
-        <v>46312.041666666664</v>
+        <v>46312.125</v>
       </c>
       <c r="L26" t="s">
         <v>43</v>
@@ -2088,16 +2082,16 @@
         <v>12</v>
       </c>
       <c r="B27" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="C27" t="s">
         <v>21</v>
       </c>
       <c r="D27" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F27" t="s">
         <v>23</v>
@@ -2106,16 +2100,16 @@
         <v>17</v>
       </c>
       <c r="H27" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I27" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="J27" s="2">
-        <v>46312.125</v>
+        <v>46311.541666666664</v>
       </c>
       <c r="K27" s="2">
-        <v>46312.666666666664</v>
+        <v>46312.083333333336</v>
       </c>
       <c r="L27" t="s">
         <v>26</v>
@@ -2126,31 +2120,34 @@
         <v>12</v>
       </c>
       <c r="B28" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="C28" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D28" t="s">
-        <v>100</v>
-      </c>
-      <c r="E28" s="1" t="s">
         <v>101</v>
       </c>
+      <c r="E28" s="1">
+        <v>26164</v>
+      </c>
       <c r="F28" t="s">
-        <v>102</v>
+        <v>68</v>
       </c>
       <c r="G28" t="s">
-        <v>17</v>
+        <v>69</v>
+      </c>
+      <c r="H28" t="s">
+        <v>69</v>
       </c>
       <c r="I28" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="J28" s="2">
-        <v>46312.5</v>
+        <v>46311.625</v>
       </c>
       <c r="K28" s="2">
-        <v>46315.75</v>
+        <v>46312.041666666664</v>
       </c>
       <c r="L28" t="s">
         <v>43</v>
@@ -2158,22 +2155,22 @@
     </row>
     <row r="29" spans="1:12">
       <c r="A29" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B29" t="s">
-        <v>61</v>
+        <v>13</v>
       </c>
       <c r="C29" t="s">
+        <v>102</v>
+      </c>
+      <c r="D29" t="s">
         <v>103</v>
       </c>
-      <c r="D29" t="s">
+      <c r="E29" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="F29" t="s">
         <v>105</v>
-      </c>
-      <c r="F29" t="s">
-        <v>64</v>
       </c>
       <c r="G29" t="s">
         <v>17</v>
@@ -2182,10 +2179,10 @@
         <v>18</v>
       </c>
       <c r="J29" s="2">
-        <v>46312.625</v>
+        <v>46312.083333333336</v>
       </c>
       <c r="K29" s="2">
-        <v>46314.75</v>
+        <v>46315.5</v>
       </c>
       <c r="L29" t="s">
         <v>43</v>
@@ -2193,107 +2190,110 @@
     </row>
     <row r="30" spans="1:12">
       <c r="A30" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B30" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C30" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="D30" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="F30" t="s">
-        <v>109</v>
+        <v>23</v>
       </c>
       <c r="G30" t="s">
-        <v>110</v>
+        <v>17</v>
+      </c>
+      <c r="H30" t="s">
+        <v>53</v>
       </c>
       <c r="I30" t="s">
-        <v>18</v>
+        <v>99</v>
       </c>
       <c r="J30" s="2">
-        <v>46312.625</v>
+        <v>46312.125</v>
       </c>
       <c r="K30" s="2">
-        <v>46313.75</v>
+        <v>46312.666666666664</v>
       </c>
       <c r="L30" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="31" spans="1:12">
       <c r="A31" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B31" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="C31" t="s">
-        <v>21</v>
+        <v>106</v>
       </c>
       <c r="D31" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="F31" t="s">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="G31" t="s">
         <v>17</v>
       </c>
       <c r="I31" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J31" s="2">
-        <v>46314.25</v>
+        <v>46312.541666666664</v>
       </c>
       <c r="K31" s="2">
-        <v>46314.75</v>
+        <v>46314.791666666664</v>
       </c>
       <c r="L31" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
     </row>
     <row r="32" spans="1:12">
       <c r="A32" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B32" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="C32" t="s">
-        <v>21</v>
+        <v>109</v>
       </c>
       <c r="D32" t="s">
+        <v>110</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F32" t="s">
+        <v>112</v>
+      </c>
+      <c r="G32" t="s">
         <v>113</v>
       </c>
-      <c r="E32" s="1">
-        <v>2</v>
-      </c>
-      <c r="F32" t="s">
-        <v>58</v>
-      </c>
-      <c r="G32" t="s">
-        <v>17</v>
-      </c>
       <c r="I32" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J32" s="2">
-        <v>46314.25</v>
+        <v>46312.625</v>
       </c>
       <c r="K32" s="2">
-        <v>46314.75</v>
+        <v>46313.75</v>
       </c>
       <c r="L32" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
     </row>
     <row r="33" spans="1:12">
@@ -2301,7 +2301,7 @@
         <v>12</v>
       </c>
       <c r="B33" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C33" t="s">
         <v>21</v>
@@ -2309,11 +2309,11 @@
       <c r="D33" t="s">
         <v>114</v>
       </c>
-      <c r="E33" s="1" t="s">
-        <v>115</v>
+      <c r="E33" s="1">
+        <v>2</v>
       </c>
       <c r="F33" t="s">
-        <v>116</v>
+        <v>62</v>
       </c>
       <c r="G33" t="s">
         <v>17</v>
@@ -2336,42 +2336,45 @@
         <v>12</v>
       </c>
       <c r="B34" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="C34" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D34" t="s">
+        <v>115</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="F34" t="s">
         <v>117</v>
-      </c>
-      <c r="E34" s="1">
-        <v>34</v>
-      </c>
-      <c r="F34" t="s">
-        <v>23</v>
       </c>
       <c r="G34" t="s">
         <v>17</v>
       </c>
       <c r="I34" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J34" s="2">
-        <v>46314.625</v>
+        <v>46314.25</v>
       </c>
       <c r="K34" s="2">
-        <v>46318.75</v>
+        <v>46314.75</v>
       </c>
       <c r="L34" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="35" spans="1:12">
       <c r="A35" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B35" t="s">
-        <v>61</v>
+        <v>59</v>
+      </c>
+      <c r="C35" t="s">
+        <v>21</v>
       </c>
       <c r="D35" t="s">
         <v>118</v>
@@ -2380,57 +2383,54 @@
         <v>119</v>
       </c>
       <c r="F35" t="s">
-        <v>120</v>
+        <v>23</v>
       </c>
       <c r="G35" t="s">
         <v>17</v>
       </c>
-      <c r="H35" t="s">
-        <v>49</v>
-      </c>
       <c r="I35" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J35" s="2">
-        <v>46314.625</v>
+        <v>46314.25</v>
       </c>
       <c r="K35" s="2">
-        <v>46315.166666666664</v>
+        <v>46314.75</v>
       </c>
       <c r="L35" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="36" spans="1:12">
       <c r="A36" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B36" t="s">
-        <v>121</v>
-      </c>
-      <c r="C36" t="s">
-        <v>122</v>
+        <v>39</v>
       </c>
       <c r="D36" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>124</v>
+        <v>41</v>
       </c>
       <c r="F36" t="s">
-        <v>125</v>
+        <v>42</v>
       </c>
       <c r="G36" t="s">
-        <v>126</v>
+        <v>17</v>
+      </c>
+      <c r="H36" t="s">
+        <v>53</v>
       </c>
       <c r="I36" t="s">
         <v>18</v>
       </c>
       <c r="J36" s="2">
-        <v>46315.208333333336</v>
+        <v>46314.625</v>
       </c>
       <c r="K36" s="2">
-        <v>46316.791666666664</v>
+        <v>46315.166666666664</v>
       </c>
       <c r="L36" t="s">
         <v>43</v>
@@ -2441,31 +2441,31 @@
         <v>12</v>
       </c>
       <c r="B37" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="C37" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="D37" t="s">
-        <v>127</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>128</v>
+        <v>121</v>
+      </c>
+      <c r="E37" s="1">
+        <v>34</v>
       </c>
       <c r="F37" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G37" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="I37" t="s">
         <v>18</v>
       </c>
       <c r="J37" s="2">
-        <v>46315.25</v>
+        <v>46314.625</v>
       </c>
       <c r="K37" s="2">
-        <v>46317.166666666664</v>
+        <v>46318.75</v>
       </c>
       <c r="L37" t="s">
         <v>43</v>
@@ -2473,34 +2473,34 @@
     </row>
     <row r="38" spans="1:12">
       <c r="A38" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B38" t="s">
-        <v>28</v>
+        <v>122</v>
       </c>
       <c r="C38" t="s">
-        <v>32</v>
+        <v>123</v>
       </c>
       <c r="D38" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="F38" t="s">
-        <v>31</v>
+        <v>126</v>
       </c>
       <c r="G38" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="I38" t="s">
         <v>18</v>
       </c>
       <c r="J38" s="2">
-        <v>46315.291666666664</v>
+        <v>46315.208333333336</v>
       </c>
       <c r="K38" s="2">
-        <v>46317.166666666664</v>
+        <v>46316.791666666664</v>
       </c>
       <c r="L38" t="s">
         <v>43</v>
@@ -2508,34 +2508,34 @@
     </row>
     <row r="39" spans="1:12">
       <c r="A39" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B39" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C39" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D39" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F39" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G39" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="I39" t="s">
         <v>18</v>
       </c>
       <c r="J39" s="2">
-        <v>46315.708333333336</v>
+        <v>46315.25</v>
       </c>
       <c r="K39" s="2">
-        <v>46317.75</v>
+        <v>46317.166666666664</v>
       </c>
       <c r="L39" t="s">
         <v>43</v>
@@ -2543,37 +2543,34 @@
     </row>
     <row r="40" spans="1:12">
       <c r="A40" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B40" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="C40" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="D40" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F40" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="G40" t="s">
-        <v>48</v>
-      </c>
-      <c r="H40" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="I40" t="s">
         <v>18</v>
       </c>
       <c r="J40" s="2">
-        <v>46316.104166666664</v>
+        <v>46315.291666666664</v>
       </c>
       <c r="K40" s="2">
-        <v>46316.916666666664</v>
+        <v>46317.166666666664</v>
       </c>
       <c r="L40" t="s">
         <v>43</v>
@@ -2581,37 +2578,37 @@
     </row>
     <row r="41" spans="1:12">
       <c r="A41" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B41" t="s">
-        <v>71</v>
+        <v>28</v>
       </c>
       <c r="C41" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="D41" t="s">
-        <v>135</v>
-      </c>
-      <c r="E41" s="1">
-        <v>63</v>
+        <v>132</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>133</v>
       </c>
       <c r="F41" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="G41" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="I41" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J41" s="2">
-        <v>46316.25</v>
+        <v>46315.708333333336</v>
       </c>
       <c r="K41" s="2">
-        <v>46316.75</v>
+        <v>46317.75</v>
       </c>
       <c r="L41" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
     </row>
     <row r="42" spans="1:12">
@@ -2619,25 +2616,22 @@
         <v>12</v>
       </c>
       <c r="B42" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="C42" t="s">
         <v>21</v>
       </c>
       <c r="D42" t="s">
-        <v>136</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
+      </c>
+      <c r="E42" s="1">
+        <v>63</v>
       </c>
       <c r="F42" t="s">
-        <v>116</v>
+        <v>23</v>
       </c>
       <c r="G42" t="s">
-        <v>17</v>
-      </c>
-      <c r="H42" t="s">
-        <v>138</v>
+        <v>24</v>
       </c>
       <c r="I42" t="s">
         <v>25</v>
@@ -2657,37 +2651,37 @@
         <v>12</v>
       </c>
       <c r="B43" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C43" t="s">
-        <v>66</v>
+        <v>21</v>
       </c>
       <c r="D43" t="s">
-        <v>67</v>
-      </c>
-      <c r="E43" s="1">
-        <v>26169</v>
+        <v>135</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>136</v>
       </c>
       <c r="F43" t="s">
-        <v>68</v>
+        <v>117</v>
       </c>
       <c r="G43" t="s">
-        <v>69</v>
+        <v>17</v>
       </c>
       <c r="H43" t="s">
-        <v>69</v>
+        <v>137</v>
       </c>
       <c r="I43" t="s">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="J43" s="2">
-        <v>46316.625</v>
+        <v>46316.25</v>
       </c>
       <c r="K43" s="2">
-        <v>46317.041666666664</v>
+        <v>46316.75</v>
       </c>
       <c r="L43" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="44" spans="1:12">
@@ -2695,31 +2689,34 @@
         <v>12</v>
       </c>
       <c r="B44" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="C44" t="s">
-        <v>99</v>
+        <v>49</v>
       </c>
       <c r="D44" t="s">
+        <v>138</v>
+      </c>
+      <c r="E44" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="E44" s="1" t="s">
-        <v>140</v>
-      </c>
       <c r="F44" t="s">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="G44" t="s">
-        <v>17</v>
+        <v>52</v>
+      </c>
+      <c r="H44" t="s">
+        <v>53</v>
       </c>
       <c r="I44" t="s">
         <v>18</v>
       </c>
       <c r="J44" s="2">
-        <v>46316.625</v>
+        <v>46316.291666666664</v>
       </c>
       <c r="K44" s="2">
-        <v>46319.75</v>
+        <v>46316.916666666664</v>
       </c>
       <c r="L44" t="s">
         <v>43</v>
@@ -2733,16 +2730,16 @@
         <v>13</v>
       </c>
       <c r="C45" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D45" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F45" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="G45" t="s">
         <v>17</v>
@@ -2765,37 +2762,37 @@
         <v>12</v>
       </c>
       <c r="B46" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C46" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="D46" t="s">
-        <v>136</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>141</v>
+        <v>67</v>
+      </c>
+      <c r="E46" s="1">
+        <v>26169</v>
       </c>
       <c r="F46" t="s">
-        <v>116</v>
+        <v>68</v>
       </c>
       <c r="G46" t="s">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="H46" t="s">
-        <v>138</v>
+        <v>69</v>
       </c>
       <c r="I46" t="s">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="J46" s="2">
-        <v>46316.791666666664</v>
+        <v>46316.625</v>
       </c>
       <c r="K46" s="2">
-        <v>46317.75</v>
+        <v>46317.041666666664</v>
       </c>
       <c r="L46" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
     </row>
     <row r="47" spans="1:12">
@@ -2803,28 +2800,31 @@
         <v>12</v>
       </c>
       <c r="B47" t="s">
-        <v>121</v>
+        <v>13</v>
+      </c>
+      <c r="C47" t="s">
+        <v>102</v>
       </c>
       <c r="D47" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F47" t="s">
-        <v>125</v>
+        <v>83</v>
       </c>
       <c r="G47" t="s">
-        <v>144</v>
+        <v>17</v>
       </c>
       <c r="I47" t="s">
         <v>18</v>
       </c>
       <c r="J47" s="2">
-        <v>46317.208333333336</v>
+        <v>46316.625</v>
       </c>
       <c r="K47" s="2">
-        <v>46318.708333333336</v>
+        <v>46319.75</v>
       </c>
       <c r="L47" t="s">
         <v>43</v>
@@ -2832,66 +2832,69 @@
     </row>
     <row r="48" spans="1:12">
       <c r="A48" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B48" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="C48" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="D48" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="F48" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="G48" t="s">
-        <v>110</v>
+        <v>17</v>
+      </c>
+      <c r="H48" t="s">
+        <v>137</v>
       </c>
       <c r="I48" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J48" s="2">
-        <v>46317.25</v>
+        <v>46316.791666666664</v>
       </c>
       <c r="K48" s="2">
-        <v>46318.166666666664</v>
+        <v>46317.75</v>
       </c>
       <c r="L48" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="49" spans="1:12">
       <c r="A49" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B49" t="s">
-        <v>28</v>
-      </c>
-      <c r="C49" t="s">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="D49" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F49" t="s">
-        <v>31</v>
+        <v>126</v>
+      </c>
+      <c r="G49" t="s">
+        <v>145</v>
       </c>
       <c r="I49" t="s">
         <v>18</v>
       </c>
       <c r="J49" s="2">
-        <v>46317.291666666664</v>
+        <v>46317.208333333336</v>
       </c>
       <c r="K49" s="2">
-        <v>46318.166666666664</v>
+        <v>46318.708333333336</v>
       </c>
       <c r="L49" t="s">
         <v>43</v>
@@ -2902,28 +2905,31 @@
         <v>27</v>
       </c>
       <c r="B50" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="C50" t="s">
-        <v>149</v>
+        <v>109</v>
       </c>
       <c r="D50" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="F50" t="s">
-        <v>82</v>
+        <v>112</v>
+      </c>
+      <c r="G50" t="s">
+        <v>113</v>
       </c>
       <c r="I50" t="s">
         <v>18</v>
       </c>
       <c r="J50" s="2">
-        <v>46317.927777777775</v>
+        <v>46317.25</v>
       </c>
       <c r="K50" s="2">
-        <v>46318.969444444447</v>
+        <v>46318.166666666664</v>
       </c>
       <c r="L50" t="s">
         <v>43</v>
@@ -2931,72 +2937,66 @@
     </row>
     <row r="51" spans="1:12">
       <c r="A51" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B51" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="C51" t="s">
-        <v>21</v>
+        <v>87</v>
       </c>
       <c r="D51" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="F51" t="s">
-        <v>23</v>
-      </c>
-      <c r="G51" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="I51" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J51" s="2">
-        <v>46318.25</v>
+        <v>46317.291666666664</v>
       </c>
       <c r="K51" s="2">
-        <v>46318.75</v>
+        <v>46318.166666666664</v>
       </c>
       <c r="L51" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
     </row>
     <row r="52" spans="1:12">
       <c r="A52" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B52" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="C52" t="s">
-        <v>21</v>
+        <v>150</v>
       </c>
       <c r="D52" t="s">
-        <v>154</v>
-      </c>
-      <c r="E52" s="1">
-        <v>4</v>
+        <v>151</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>152</v>
       </c>
       <c r="F52" t="s">
-        <v>58</v>
-      </c>
-      <c r="G52" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="I52" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J52" s="2">
-        <v>46318.25</v>
+        <v>46317.927777777775</v>
       </c>
       <c r="K52" s="2">
-        <v>46318.75</v>
+        <v>46318.969444444447</v>
       </c>
       <c r="L52" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
     </row>
     <row r="53" spans="1:12">
@@ -3004,69 +3004,69 @@
         <v>12</v>
       </c>
       <c r="B53" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="C53" t="s">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="D53" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F53" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="G53" t="s">
-        <v>48</v>
-      </c>
-      <c r="H53" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="I53" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J53" s="2">
-        <v>46318.291666666664</v>
+        <v>46318.25</v>
       </c>
       <c r="K53" s="2">
-        <v>46319.125</v>
+        <v>46318.75</v>
       </c>
       <c r="L53" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="54" spans="1:12">
       <c r="A54" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B54" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C54" t="s">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="D54" t="s">
-        <v>157</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
+      </c>
+      <c r="E54" s="1">
+        <v>4</v>
       </c>
       <c r="F54" t="s">
-        <v>91</v>
+        <v>62</v>
+      </c>
+      <c r="G54" t="s">
+        <v>17</v>
       </c>
       <c r="I54" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J54" s="2">
-        <v>46318.291666666664</v>
+        <v>46318.25</v>
       </c>
       <c r="K54" s="2">
-        <v>46319.666666666664</v>
+        <v>46318.75</v>
       </c>
       <c r="L54" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="55" spans="1:12">
@@ -3074,28 +3074,34 @@
         <v>27</v>
       </c>
       <c r="B55" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="C55" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D55" t="s">
+        <v>156</v>
+      </c>
+      <c r="E55" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="E55" s="1" t="s">
-        <v>158</v>
-      </c>
       <c r="F55" t="s">
-        <v>91</v>
+        <v>94</v>
+      </c>
+      <c r="G55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H55" t="s">
+        <v>53</v>
       </c>
       <c r="I55" t="s">
         <v>18</v>
       </c>
       <c r="J55" s="2">
-        <v>46318.291666666664</v>
+        <v>46318.25</v>
       </c>
       <c r="K55" s="2">
-        <v>46319.666666666664</v>
+        <v>46319.166666666664</v>
       </c>
       <c r="L55" t="s">
         <v>43</v>
@@ -3106,34 +3112,34 @@
         <v>12</v>
       </c>
       <c r="B56" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="C56" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D56" t="s">
-        <v>98</v>
-      </c>
-      <c r="E56" s="1">
-        <v>26168</v>
+        <v>158</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>159</v>
       </c>
       <c r="F56" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="G56" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="H56" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="I56" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="J56" s="2">
-        <v>46318.625</v>
+        <v>46318.291666666664</v>
       </c>
       <c r="K56" s="2">
-        <v>46319.041666666664</v>
+        <v>46319.125</v>
       </c>
       <c r="L56" t="s">
         <v>43</v>
@@ -3144,28 +3150,34 @@
         <v>12</v>
       </c>
       <c r="B57" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="C57" t="s">
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="D57" t="s">
-        <v>159</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>156</v>
+        <v>101</v>
+      </c>
+      <c r="E57" s="1">
+        <v>26168</v>
       </c>
       <c r="F57" t="s">
-        <v>48</v>
+        <v>68</v>
+      </c>
+      <c r="G57" t="s">
+        <v>69</v>
+      </c>
+      <c r="H57" t="s">
+        <v>69</v>
       </c>
       <c r="I57" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="J57" s="2">
-        <v>46318.704861111109</v>
+        <v>46318.625</v>
       </c>
       <c r="K57" s="2">
-        <v>46319.204861111109</v>
+        <v>46319.041666666664</v>
       </c>
       <c r="L57" t="s">
         <v>43</v>
@@ -3176,34 +3188,31 @@
         <v>12</v>
       </c>
       <c r="B58" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="C58" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="D58" t="s">
         <v>160</v>
       </c>
-      <c r="E58" s="1">
-        <v>1</v>
+      <c r="E58" s="1" t="s">
+        <v>159</v>
       </c>
       <c r="F58" t="s">
-        <v>161</v>
-      </c>
-      <c r="G58" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="I58" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J58" s="2">
-        <v>46319.25</v>
+        <v>46318.704861111109</v>
       </c>
       <c r="K58" s="2">
-        <v>46322.75</v>
+        <v>46319.204861111109</v>
       </c>
       <c r="L58" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
     </row>
     <row r="59" spans="1:12">
@@ -3211,19 +3220,19 @@
         <v>12</v>
       </c>
       <c r="B59" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="C59" t="s">
         <v>21</v>
       </c>
       <c r="D59" t="s">
+        <v>161</v>
+      </c>
+      <c r="E59" s="1">
+        <v>1</v>
+      </c>
+      <c r="F59" t="s">
         <v>162</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="F59" t="s">
-        <v>116</v>
       </c>
       <c r="G59" t="s">
         <v>17</v>
@@ -3235,7 +3244,7 @@
         <v>46319.25</v>
       </c>
       <c r="K59" s="2">
-        <v>46319.75</v>
+        <v>46322.75</v>
       </c>
       <c r="L59" t="s">
         <v>26</v>
@@ -3246,31 +3255,34 @@
         <v>12</v>
       </c>
       <c r="B60" t="s">
-        <v>121</v>
+        <v>59</v>
       </c>
       <c r="C60" t="s">
-        <v>122</v>
+        <v>21</v>
       </c>
       <c r="D60" t="s">
+        <v>163</v>
+      </c>
+      <c r="E60" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="E60" s="1" t="s">
-        <v>165</v>
-      </c>
       <c r="F60" t="s">
-        <v>125</v>
+        <v>117</v>
+      </c>
+      <c r="G60" t="s">
+        <v>17</v>
       </c>
       <c r="I60" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J60" s="2">
-        <v>46320</v>
+        <v>46319.25</v>
       </c>
       <c r="K60" s="2">
-        <v>46322</v>
+        <v>46319.75</v>
       </c>
       <c r="L60" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="61" spans="1:12">
@@ -3278,28 +3290,31 @@
         <v>27</v>
       </c>
       <c r="B61" t="s">
-        <v>61</v>
-      </c>
-      <c r="C61" t="s">
-        <v>103</v>
+        <v>39</v>
       </c>
       <c r="D61" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>167</v>
+        <v>41</v>
       </c>
       <c r="F61" t="s">
-        <v>64</v>
+        <v>42</v>
+      </c>
+      <c r="G61" t="s">
+        <v>17</v>
+      </c>
+      <c r="H61" t="s">
+        <v>53</v>
       </c>
       <c r="I61" t="s">
         <v>18</v>
       </c>
       <c r="J61" s="2">
-        <v>46320.21875</v>
+        <v>46319.625</v>
       </c>
       <c r="K61" s="2">
-        <v>46324.59375</v>
+        <v>46320.166666666664</v>
       </c>
       <c r="L61" t="s">
         <v>43</v>
@@ -3310,31 +3325,28 @@
         <v>12</v>
       </c>
       <c r="B62" t="s">
-        <v>35</v>
+        <v>122</v>
       </c>
       <c r="C62" t="s">
-        <v>50</v>
+        <v>123</v>
       </c>
       <c r="D62" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F62" t="s">
-        <v>16</v>
-      </c>
-      <c r="G62" t="s">
-        <v>24</v>
+        <v>126</v>
       </c>
       <c r="I62" t="s">
         <v>18</v>
       </c>
       <c r="J62" s="2">
-        <v>46321.208333333336</v>
+        <v>46320</v>
       </c>
       <c r="K62" s="2">
-        <v>46323.166666666664</v>
+        <v>46322</v>
       </c>
       <c r="L62" t="s">
         <v>43</v>
@@ -3345,28 +3357,28 @@
         <v>27</v>
       </c>
       <c r="B63" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C63" t="s">
-        <v>32</v>
+        <v>106</v>
       </c>
       <c r="D63" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F63" t="s">
-        <v>31</v>
+        <v>86</v>
       </c>
       <c r="I63" t="s">
         <v>18</v>
       </c>
       <c r="J63" s="2">
-        <v>46321.21875</v>
+        <v>46320.21875</v>
       </c>
       <c r="K63" s="2">
-        <v>46323.21875</v>
+        <v>46324.59375</v>
       </c>
       <c r="L63" t="s">
         <v>43</v>
@@ -3380,13 +3392,13 @@
         <v>35</v>
       </c>
       <c r="C64" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="D64" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F64" t="s">
         <v>16</v>
@@ -3398,7 +3410,7 @@
         <v>18</v>
       </c>
       <c r="J64" s="2">
-        <v>46321.25</v>
+        <v>46321.208333333336</v>
       </c>
       <c r="K64" s="2">
         <v>46323.166666666664</v>
@@ -3409,34 +3421,31 @@
     </row>
     <row r="65" spans="1:12">
       <c r="A65" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B65" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="C65" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D65" t="s">
-        <v>174</v>
-      </c>
-      <c r="E65" s="1">
-        <v>21</v>
+        <v>172</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>173</v>
       </c>
       <c r="F65" t="s">
-        <v>16</v>
-      </c>
-      <c r="G65" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="I65" t="s">
         <v>18</v>
       </c>
       <c r="J65" s="2">
-        <v>46321.625</v>
+        <v>46321.21875</v>
       </c>
       <c r="K65" s="2">
-        <v>46325.75</v>
+        <v>46323.21875</v>
       </c>
       <c r="L65" t="s">
         <v>43</v>
@@ -3447,57 +3456,66 @@
         <v>12</v>
       </c>
       <c r="B66" t="s">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="C66" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="D66" t="s">
+        <v>174</v>
+      </c>
+      <c r="E66" s="1" t="s">
         <v>175</v>
       </c>
       <c r="F66" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="G66" t="s">
         <v>24</v>
       </c>
-      <c r="H66" t="s">
-        <v>74</v>
-      </c>
       <c r="I66" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J66" s="2">
-        <v>46322.25</v>
+        <v>46321.25</v>
       </c>
       <c r="K66" s="2">
-        <v>46322.75</v>
+        <v>46323.166666666664</v>
       </c>
       <c r="L66" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
     </row>
     <row r="67" spans="1:12">
       <c r="A67" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B67" t="s">
-        <v>61</v>
+        <v>13</v>
+      </c>
+      <c r="C67" t="s">
+        <v>14</v>
       </c>
       <c r="D67" t="s">
         <v>176</v>
       </c>
+      <c r="E67" s="1">
+        <v>21</v>
+      </c>
       <c r="F67" t="s">
-        <v>120</v>
+        <v>16</v>
+      </c>
+      <c r="G67" t="s">
+        <v>17</v>
       </c>
       <c r="I67" t="s">
         <v>18</v>
       </c>
       <c r="J67" s="2">
-        <v>46322.256249999999</v>
+        <v>46321.625</v>
       </c>
       <c r="K67" s="2">
-        <v>46323.381249999999</v>
+        <v>46325.75</v>
       </c>
       <c r="L67" t="s">
         <v>43</v>
@@ -3508,7 +3526,7 @@
         <v>12</v>
       </c>
       <c r="B68" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="C68" t="s">
         <v>21</v>
@@ -3516,23 +3534,23 @@
       <c r="D68" t="s">
         <v>177</v>
       </c>
-      <c r="E68" s="1" t="s">
-        <v>178</v>
-      </c>
       <c r="F68" t="s">
-        <v>23</v>
+        <v>73</v>
       </c>
       <c r="G68" t="s">
-        <v>17</v>
+        <v>24</v>
+      </c>
+      <c r="H68" t="s">
+        <v>74</v>
       </c>
       <c r="I68" t="s">
         <v>25</v>
       </c>
       <c r="J68" s="2">
-        <v>46323.25</v>
+        <v>46322.25</v>
       </c>
       <c r="K68" s="2">
-        <v>46323.75</v>
+        <v>46322.75</v>
       </c>
       <c r="L68" t="s">
         <v>26</v>
@@ -3543,25 +3561,31 @@
         <v>12</v>
       </c>
       <c r="B69" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="C69" t="s">
-        <v>45</v>
+        <v>102</v>
       </c>
       <c r="D69" t="s">
-        <v>87</v>
+        <v>178</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>179</v>
       </c>
       <c r="F69" t="s">
-        <v>48</v>
+        <v>83</v>
+      </c>
+      <c r="G69" t="s">
+        <v>17</v>
       </c>
       <c r="I69" t="s">
         <v>18</v>
       </c>
       <c r="J69" s="2">
-        <v>46323.291666666664</v>
+        <v>46322.625</v>
       </c>
       <c r="K69" s="2">
-        <v>46323.791666666664</v>
+        <v>46325.75</v>
       </c>
       <c r="L69" t="s">
         <v>43</v>
@@ -3572,31 +3596,34 @@
         <v>12</v>
       </c>
       <c r="B70" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="C70" t="s">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="D70" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F70" t="s">
-        <v>181</v>
+        <v>23</v>
+      </c>
+      <c r="G70" t="s">
+        <v>17</v>
       </c>
       <c r="I70" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J70" s="2">
-        <v>46323.622916666667</v>
+        <v>46323.25</v>
       </c>
       <c r="K70" s="2">
-        <v>46324.875</v>
+        <v>46323.75</v>
       </c>
       <c r="L70" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="71" spans="1:12">
@@ -3604,34 +3631,25 @@
         <v>12</v>
       </c>
       <c r="B71" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="C71" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="D71" t="s">
-        <v>67</v>
-      </c>
-      <c r="E71" s="1">
-        <v>26173</v>
+        <v>90</v>
       </c>
       <c r="F71" t="s">
-        <v>68</v>
-      </c>
-      <c r="G71" t="s">
-        <v>69</v>
-      </c>
-      <c r="H71" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="I71" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="J71" s="2">
-        <v>46323.625</v>
+        <v>46323.291666666664</v>
       </c>
       <c r="K71" s="2">
-        <v>46324.041666666664</v>
+        <v>46323.791666666664</v>
       </c>
       <c r="L71" t="s">
         <v>43</v>
@@ -3642,28 +3660,34 @@
         <v>12</v>
       </c>
       <c r="B72" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="C72" t="s">
-        <v>14</v>
+        <v>66</v>
       </c>
       <c r="D72" t="s">
-        <v>182</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>183</v>
+        <v>67</v>
+      </c>
+      <c r="E72" s="1">
+        <v>26173</v>
       </c>
       <c r="F72" t="s">
-        <v>23</v>
+        <v>68</v>
+      </c>
+      <c r="G72" t="s">
+        <v>69</v>
+      </c>
+      <c r="H72" t="s">
+        <v>69</v>
       </c>
       <c r="I72" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="J72" s="2">
         <v>46323.625</v>
       </c>
       <c r="K72" s="2">
-        <v>46327.541666666664</v>
+        <v>46324.041666666664</v>
       </c>
       <c r="L72" t="s">
         <v>43</v>
@@ -3706,16 +3730,16 @@
         <v>12</v>
       </c>
       <c r="B74" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="C74" t="s">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="D74" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="F74" t="s">
         <v>23</v>
@@ -3724,10 +3748,10 @@
         <v>18</v>
       </c>
       <c r="J74" s="2">
-        <v>46323.661111111112</v>
+        <v>46323.625</v>
       </c>
       <c r="K74" s="2">
-        <v>46327.202777777777</v>
+        <v>46327.541666666664</v>
       </c>
       <c r="L74" t="s">
         <v>43</v>
@@ -3741,7 +3765,7 @@
         <v>35</v>
       </c>
       <c r="C75" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D75" t="s">
         <v>184</v>
@@ -3770,34 +3794,31 @@
         <v>12</v>
       </c>
       <c r="B76" t="s">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="C76" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="D76" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="F76" t="s">
         <v>23</v>
       </c>
-      <c r="G76" t="s">
-        <v>17</v>
-      </c>
       <c r="I76" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J76" s="2">
-        <v>46323.791666666664</v>
+        <v>46323.661111111112</v>
       </c>
       <c r="K76" s="2">
-        <v>46324.75</v>
+        <v>46327.202777777777</v>
       </c>
       <c r="L76" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
     </row>
     <row r="77" spans="1:12">
@@ -3805,57 +3826,60 @@
         <v>12</v>
       </c>
       <c r="B77" t="s">
-        <v>121</v>
+        <v>71</v>
+      </c>
+      <c r="C77" t="s">
+        <v>21</v>
       </c>
       <c r="D77" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="F77" t="s">
-        <v>125</v>
+        <v>23</v>
+      </c>
+      <c r="G77" t="s">
+        <v>17</v>
       </c>
       <c r="I77" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J77" s="2">
-        <v>46324</v>
+        <v>46323.791666666664</v>
       </c>
       <c r="K77" s="2">
-        <v>46326</v>
+        <v>46324.75</v>
       </c>
       <c r="L77" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="78" spans="1:12">
       <c r="A78" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B78" t="s">
-        <v>28</v>
-      </c>
-      <c r="C78" t="s">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="D78" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F78" t="s">
-        <v>31</v>
+        <v>126</v>
       </c>
       <c r="I78" t="s">
         <v>18</v>
       </c>
       <c r="J78" s="2">
-        <v>46325.003472222219</v>
+        <v>46324</v>
       </c>
       <c r="K78" s="2">
-        <v>46325.878472222219</v>
+        <v>46326</v>
       </c>
       <c r="L78" t="s">
         <v>43</v>
@@ -3866,28 +3890,28 @@
         <v>27</v>
       </c>
       <c r="B79" t="s">
-        <v>61</v>
+        <v>28</v>
       </c>
       <c r="C79" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D79" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F79" t="s">
-        <v>82</v>
+        <v>31</v>
       </c>
       <c r="I79" t="s">
         <v>18</v>
       </c>
       <c r="J79" s="2">
-        <v>46325.056944444441</v>
+        <v>46325.003472222219</v>
       </c>
       <c r="K79" s="2">
-        <v>46326.098611111112</v>
+        <v>46325.878472222219</v>
       </c>
       <c r="L79" t="s">
         <v>43</v>
@@ -3895,37 +3919,34 @@
     </row>
     <row r="80" spans="1:12">
       <c r="A80" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B80" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="C80" t="s">
-        <v>21</v>
+        <v>75</v>
       </c>
       <c r="D80" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F80" t="s">
-        <v>23</v>
-      </c>
-      <c r="G80" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="I80" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J80" s="2">
-        <v>46325.25</v>
+        <v>46325.056944444441</v>
       </c>
       <c r="K80" s="2">
-        <v>46325.75</v>
+        <v>46326.098611111112</v>
       </c>
       <c r="L80" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
     </row>
     <row r="81" spans="1:12">
@@ -3933,28 +3954,34 @@
         <v>12</v>
       </c>
       <c r="B81" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="C81" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="D81" t="s">
-        <v>133</v>
+        <v>192</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>193</v>
       </c>
       <c r="F81" t="s">
-        <v>48</v>
+        <v>23</v>
+      </c>
+      <c r="G81" t="s">
+        <v>17</v>
       </c>
       <c r="I81" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J81" s="2">
-        <v>46325.333333333336</v>
+        <v>46325.25</v>
       </c>
       <c r="K81" s="2">
-        <v>46325.833333333336</v>
+        <v>46325.75</v>
       </c>
       <c r="L81" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="82" spans="1:12">
@@ -3962,34 +3989,25 @@
         <v>12</v>
       </c>
       <c r="B82" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="C82" t="s">
-        <v>97</v>
+        <v>49</v>
       </c>
       <c r="D82" t="s">
-        <v>98</v>
-      </c>
-      <c r="E82" s="1">
-        <v>26172</v>
+        <v>138</v>
       </c>
       <c r="F82" t="s">
-        <v>68</v>
-      </c>
-      <c r="G82" t="s">
-        <v>69</v>
-      </c>
-      <c r="H82" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="I82" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="J82" s="2">
-        <v>46325.625</v>
+        <v>46325.333333333336</v>
       </c>
       <c r="K82" s="2">
-        <v>46326.041666666664</v>
+        <v>46325.833333333336</v>
       </c>
       <c r="L82" t="s">
         <v>43</v>
@@ -4000,101 +4018,104 @@
         <v>12</v>
       </c>
       <c r="B83" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C83" t="s">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="D83" t="s">
-        <v>192</v>
-      </c>
-      <c r="E83" s="1" t="s">
-        <v>193</v>
+        <v>101</v>
+      </c>
+      <c r="E83" s="1">
+        <v>26172</v>
       </c>
       <c r="F83" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="G83" t="s">
-        <v>17</v>
+        <v>69</v>
+      </c>
+      <c r="H83" t="s">
+        <v>69</v>
       </c>
       <c r="I83" t="s">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="J83" s="2">
-        <v>46325.791666666664</v>
+        <v>46325.625</v>
       </c>
       <c r="K83" s="2">
-        <v>46326.75</v>
+        <v>46326.041666666664</v>
       </c>
       <c r="L83" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
     </row>
     <row r="84" spans="1:12">
       <c r="A84" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B84" t="s">
-        <v>28</v>
+        <v>71</v>
       </c>
       <c r="C84" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="D84" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F84" t="s">
-        <v>31</v>
+        <v>23</v>
+      </c>
+      <c r="G84" t="s">
+        <v>17</v>
       </c>
       <c r="I84" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J84" s="2">
-        <v>46326.166666666664</v>
+        <v>46325.791666666664</v>
       </c>
       <c r="K84" s="2">
-        <v>46328.125</v>
+        <v>46326.75</v>
       </c>
       <c r="L84" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="85" spans="1:12">
       <c r="A85" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B85" t="s">
-        <v>71</v>
+        <v>28</v>
       </c>
       <c r="C85" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="D85" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F85" t="s">
-        <v>23</v>
-      </c>
-      <c r="G85" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="I85" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J85" s="2">
-        <v>46326.25</v>
+        <v>46326.166666666664</v>
       </c>
       <c r="K85" s="2">
-        <v>46326.75</v>
+        <v>46328.125</v>
       </c>
       <c r="L85" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
     </row>
     <row r="86" spans="1:12">
@@ -4102,28 +4123,34 @@
         <v>12</v>
       </c>
       <c r="B86" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="C86" t="s">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="D86" t="s">
-        <v>93</v>
+        <v>196</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>197</v>
       </c>
       <c r="F86" t="s">
-        <v>48</v>
+        <v>23</v>
+      </c>
+      <c r="G86" t="s">
+        <v>17</v>
       </c>
       <c r="I86" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J86" s="2">
-        <v>46326.416666666664</v>
+        <v>46326.25</v>
       </c>
       <c r="K86" s="2">
         <v>46326.75</v>
       </c>
       <c r="L86" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="87" spans="1:12">
@@ -4131,28 +4158,25 @@
         <v>12</v>
       </c>
       <c r="B87" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="C87" t="s">
-        <v>50</v>
+        <v>95</v>
       </c>
       <c r="D87" t="s">
-        <v>198</v>
-      </c>
-      <c r="E87" s="1" t="s">
-        <v>199</v>
+        <v>96</v>
       </c>
       <c r="F87" t="s">
-        <v>181</v>
+        <v>52</v>
       </c>
       <c r="I87" t="s">
         <v>18</v>
       </c>
       <c r="J87" s="2">
-        <v>46326.833333333336</v>
+        <v>46326.416666666664</v>
       </c>
       <c r="K87" s="2">
-        <v>46329.583333333336</v>
+        <v>46326.75</v>
       </c>
       <c r="L87" t="s">
         <v>43</v>
@@ -4160,31 +4184,31 @@
     </row>
     <row r="88" spans="1:12">
       <c r="A88" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B88" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="C88" t="s">
-        <v>103</v>
+        <v>54</v>
       </c>
       <c r="D88" t="s">
+        <v>198</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="F88" t="s">
         <v>200</v>
       </c>
-      <c r="E88" s="1">
-        <v>69</v>
-      </c>
-      <c r="F88" t="s">
-        <v>64</v>
-      </c>
       <c r="I88" t="s">
         <v>18</v>
       </c>
       <c r="J88" s="2">
-        <v>46327.166666666664</v>
+        <v>46326.833333333336</v>
       </c>
       <c r="K88" s="2">
-        <v>46328.541666666664</v>
+        <v>46329.583333333336</v>
       </c>
       <c r="L88" t="s">
         <v>43</v>
@@ -4192,98 +4216,95 @@
     </row>
     <row r="89" spans="1:12">
       <c r="A89" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B89" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="C89" t="s">
-        <v>21</v>
+        <v>106</v>
       </c>
       <c r="D89" t="s">
         <v>201</v>
       </c>
-      <c r="E89" s="1" t="s">
-        <v>202</v>
+      <c r="E89" s="1">
+        <v>69</v>
       </c>
       <c r="F89" t="s">
-        <v>116</v>
-      </c>
-      <c r="G89" t="s">
-        <v>17</v>
+        <v>86</v>
       </c>
       <c r="I89" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J89" s="2">
-        <v>46327.25</v>
+        <v>46327.166666666664</v>
       </c>
       <c r="K89" s="2">
-        <v>46327.75</v>
+        <v>46328.541666666664</v>
       </c>
       <c r="L89" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
     </row>
     <row r="90" spans="1:12">
       <c r="A90" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B90" t="s">
-        <v>61</v>
+        <v>59</v>
+      </c>
+      <c r="C90" t="s">
+        <v>21</v>
       </c>
       <c r="D90" t="s">
+        <v>202</v>
+      </c>
+      <c r="E90" s="1" t="s">
         <v>203</v>
       </c>
       <c r="F90" t="s">
-        <v>120</v>
+        <v>117</v>
+      </c>
+      <c r="G90" t="s">
+        <v>17</v>
       </c>
       <c r="I90" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J90" s="2">
-        <v>46327.708333333336</v>
+        <v>46327.25</v>
       </c>
       <c r="K90" s="2">
-        <v>46328.833333333336</v>
+        <v>46327.75</v>
       </c>
       <c r="L90" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="91" spans="1:12">
       <c r="A91" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B91" t="s">
-        <v>71</v>
-      </c>
-      <c r="C91" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="D91" t="s">
-        <v>201</v>
-      </c>
-      <c r="E91" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F91" t="s">
-        <v>116</v>
-      </c>
-      <c r="G91" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="I91" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J91" s="2">
-        <v>46327.791666666664</v>
+        <v>46327.708333333336</v>
       </c>
       <c r="K91" s="2">
-        <v>46328.75</v>
+        <v>46328.833333333336</v>
       </c>
       <c r="L91" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
     </row>
     <row r="92" spans="1:12">
@@ -4291,31 +4312,34 @@
         <v>12</v>
       </c>
       <c r="B92" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="C92" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="D92" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F92" t="s">
-        <v>23</v>
+        <v>117</v>
+      </c>
+      <c r="G92" t="s">
+        <v>17</v>
       </c>
       <c r="I92" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J92" s="2">
-        <v>46327.904861111114</v>
+        <v>46327.791666666664</v>
       </c>
       <c r="K92" s="2">
-        <v>46331.196527777778</v>
+        <v>46328.75</v>
       </c>
       <c r="L92" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="93" spans="1:12">
@@ -4323,28 +4347,28 @@
         <v>12</v>
       </c>
       <c r="B93" t="s">
-        <v>121</v>
+        <v>35</v>
       </c>
       <c r="C93" t="s">
-        <v>122</v>
+        <v>36</v>
       </c>
       <c r="D93" t="s">
+        <v>205</v>
+      </c>
+      <c r="E93" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="E93" s="1" t="s">
-        <v>207</v>
-      </c>
       <c r="F93" t="s">
-        <v>125</v>
+        <v>23</v>
       </c>
       <c r="I93" t="s">
         <v>18</v>
       </c>
       <c r="J93" s="2">
-        <v>46329</v>
+        <v>46327.904861111114</v>
       </c>
       <c r="K93" s="2">
-        <v>46330</v>
+        <v>46331.196527777778</v>
       </c>
       <c r="L93" t="s">
         <v>43</v>
@@ -4355,28 +4379,28 @@
         <v>12</v>
       </c>
       <c r="B94" t="s">
-        <v>13</v>
+        <v>122</v>
       </c>
       <c r="C94" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="D94" t="s">
+        <v>207</v>
+      </c>
+      <c r="E94" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="E94" s="1" t="s">
-        <v>209</v>
-      </c>
       <c r="F94" t="s">
-        <v>181</v>
+        <v>126</v>
       </c>
       <c r="I94" t="s">
         <v>18</v>
       </c>
       <c r="J94" s="2">
-        <v>46329.333333333336</v>
+        <v>46329</v>
       </c>
       <c r="K94" s="2">
-        <v>46332.625</v>
+        <v>46330</v>
       </c>
       <c r="L94" t="s">
         <v>43</v>
@@ -4384,25 +4408,31 @@
     </row>
     <row r="95" spans="1:12">
       <c r="A95" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B95" t="s">
-        <v>61</v>
+        <v>13</v>
+      </c>
+      <c r="C95" t="s">
+        <v>102</v>
       </c>
       <c r="D95" t="s">
+        <v>209</v>
+      </c>
+      <c r="E95" s="1" t="s">
         <v>210</v>
       </c>
       <c r="F95" t="s">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="I95" t="s">
         <v>18</v>
       </c>
       <c r="J95" s="2">
-        <v>46330.083333333336</v>
+        <v>46329.333333333336</v>
       </c>
       <c r="K95" s="2">
-        <v>46331.208333333336</v>
+        <v>46332.625</v>
       </c>
       <c r="L95" t="s">
         <v>43</v>
@@ -4410,28 +4440,25 @@
     </row>
     <row r="96" spans="1:12">
       <c r="A96" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B96" t="s">
-        <v>65</v>
-      </c>
-      <c r="C96" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="D96" t="s">
-        <v>67</v>
+        <v>211</v>
       </c>
       <c r="F96" t="s">
-        <v>68</v>
+        <v>42</v>
       </c>
       <c r="I96" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="J96" s="2">
-        <v>46330.625</v>
+        <v>46330.083333333336</v>
       </c>
       <c r="K96" s="2">
-        <v>46331.125</v>
+        <v>46331.208333333336</v>
       </c>
       <c r="L96" t="s">
         <v>43</v>
@@ -4442,28 +4469,25 @@
         <v>12</v>
       </c>
       <c r="B97" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="C97" t="s">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="D97" t="s">
-        <v>211</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>212</v>
+        <v>67</v>
       </c>
       <c r="F97" t="s">
-        <v>181</v>
+        <v>68</v>
       </c>
       <c r="I97" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="J97" s="2">
-        <v>46330.633333333331</v>
+        <v>46330.625</v>
       </c>
       <c r="K97" s="2">
-        <v>46333.925000000003</v>
+        <v>46331.125</v>
       </c>
       <c r="L97" t="s">
         <v>43</v>
@@ -4477,16 +4501,16 @@
         <v>13</v>
       </c>
       <c r="C98" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D98" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F98" t="s">
-        <v>181</v>
+        <v>200</v>
       </c>
       <c r="I98" t="s">
         <v>18</v>
@@ -4506,25 +4530,28 @@
         <v>12</v>
       </c>
       <c r="B99" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="C99" t="s">
-        <v>45</v>
+        <v>102</v>
       </c>
       <c r="D99" t="s">
-        <v>159</v>
+        <v>212</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>213</v>
       </c>
       <c r="F99" t="s">
-        <v>48</v>
+        <v>200</v>
       </c>
       <c r="I99" t="s">
         <v>18</v>
       </c>
       <c r="J99" s="2">
-        <v>46330.704861111109</v>
+        <v>46330.633333333331</v>
       </c>
       <c r="K99" s="2">
-        <v>46331.204861111109</v>
+        <v>46333.925000000003</v>
       </c>
       <c r="L99" t="s">
         <v>43</v>
@@ -4532,31 +4559,28 @@
     </row>
     <row r="100" spans="1:12">
       <c r="A100" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B100" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="C100" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="D100" t="s">
-        <v>213</v>
-      </c>
-      <c r="E100" s="1" t="s">
-        <v>214</v>
+        <v>160</v>
       </c>
       <c r="F100" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="I100" t="s">
         <v>18</v>
       </c>
       <c r="J100" s="2">
-        <v>46330.75</v>
+        <v>46330.704861111109</v>
       </c>
       <c r="K100" s="2">
-        <v>46332.75</v>
+        <v>46331.204861111109</v>
       </c>
       <c r="L100" t="s">
         <v>43</v>
@@ -4567,28 +4591,28 @@
         <v>27</v>
       </c>
       <c r="B101" t="s">
-        <v>61</v>
+        <v>28</v>
       </c>
       <c r="C101" t="s">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="D101" t="s">
+        <v>214</v>
+      </c>
+      <c r="E101" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="E101" s="1" t="s">
-        <v>216</v>
-      </c>
       <c r="F101" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="I101" t="s">
         <v>18</v>
       </c>
       <c r="J101" s="2">
-        <v>46331.020833333336</v>
+        <v>46330.75</v>
       </c>
       <c r="K101" s="2">
-        <v>46332.520833333336</v>
+        <v>46332.75</v>
       </c>
       <c r="L101" t="s">
         <v>43</v>
@@ -4599,25 +4623,28 @@
         <v>27</v>
       </c>
       <c r="B102" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C102" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D102" t="s">
+        <v>216</v>
+      </c>
+      <c r="E102" s="1" t="s">
         <v>217</v>
       </c>
       <c r="F102" t="s">
-        <v>31</v>
+        <v>86</v>
       </c>
       <c r="I102" t="s">
         <v>18</v>
       </c>
       <c r="J102" s="2">
-        <v>46331.291666666664</v>
+        <v>46331.020833333336</v>
       </c>
       <c r="K102" s="2">
-        <v>46332.166666666664</v>
+        <v>46332.520833333336</v>
       </c>
       <c r="L102" t="s">
         <v>43</v>
@@ -4625,31 +4652,28 @@
     </row>
     <row r="103" spans="1:12">
       <c r="A103" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B103" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="C103" t="s">
-        <v>36</v>
+        <v>87</v>
       </c>
       <c r="D103" t="s">
         <v>218</v>
       </c>
-      <c r="E103" s="1" t="s">
-        <v>219</v>
-      </c>
       <c r="F103" t="s">
-        <v>181</v>
+        <v>31</v>
       </c>
       <c r="I103" t="s">
         <v>18</v>
       </c>
       <c r="J103" s="2">
-        <v>46331.496527777781</v>
+        <v>46331.291666666664</v>
       </c>
       <c r="K103" s="2">
-        <v>46334.746527777781</v>
+        <v>46332.166666666664</v>
       </c>
       <c r="L103" t="s">
         <v>43</v>
@@ -4666,13 +4690,13 @@
         <v>36</v>
       </c>
       <c r="D104" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F104" t="s">
-        <v>181</v>
+        <v>200</v>
       </c>
       <c r="I104" t="s">
         <v>18</v>
@@ -4689,31 +4713,31 @@
     </row>
     <row r="105" spans="1:12">
       <c r="A105" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B105" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="C105" t="s">
-        <v>149</v>
+        <v>36</v>
       </c>
       <c r="D105" t="s">
+        <v>219</v>
+      </c>
+      <c r="E105" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="E105" s="1" t="s">
-        <v>221</v>
-      </c>
       <c r="F105" t="s">
-        <v>82</v>
+        <v>200</v>
       </c>
       <c r="I105" t="s">
         <v>18</v>
       </c>
       <c r="J105" s="2">
-        <v>46332.056250000001</v>
+        <v>46331.496527777781</v>
       </c>
       <c r="K105" s="2">
-        <v>46332.597916666666</v>
+        <v>46334.746527777781</v>
       </c>
       <c r="L105" t="s">
         <v>43</v>
@@ -4724,28 +4748,28 @@
         <v>27</v>
       </c>
       <c r="B106" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="C106" t="s">
-        <v>106</v>
+        <v>150</v>
       </c>
       <c r="D106" t="s">
+        <v>221</v>
+      </c>
+      <c r="E106" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="E106" s="1" t="s">
-        <v>223</v>
-      </c>
       <c r="F106" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="I106" t="s">
         <v>18</v>
       </c>
       <c r="J106" s="2">
-        <v>46332.083333333336</v>
+        <v>46332.056250000001</v>
       </c>
       <c r="K106" s="2">
-        <v>46333.291666666664</v>
+        <v>46332.597916666666</v>
       </c>
       <c r="L106" t="s">
         <v>43</v>
@@ -4753,37 +4777,34 @@
     </row>
     <row r="107" spans="1:12">
       <c r="A107" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B107" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="C107" t="s">
-        <v>21</v>
+        <v>109</v>
       </c>
       <c r="D107" t="s">
+        <v>223</v>
+      </c>
+      <c r="E107" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="E107" s="1">
-        <v>10</v>
-      </c>
       <c r="F107" t="s">
-        <v>58</v>
-      </c>
-      <c r="G107" t="s">
-        <v>17</v>
+        <v>112</v>
       </c>
       <c r="I107" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J107" s="2">
-        <v>46332.25</v>
+        <v>46332.083333333336</v>
       </c>
       <c r="K107" s="2">
-        <v>46332.75</v>
+        <v>46333.291666666664</v>
       </c>
       <c r="L107" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
     </row>
     <row r="108" spans="1:12">
@@ -4791,7 +4812,7 @@
         <v>12</v>
       </c>
       <c r="B108" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="C108" t="s">
         <v>21</v>
@@ -4800,10 +4821,10 @@
         <v>225</v>
       </c>
       <c r="E108" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F108" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G108" t="s">
         <v>17</v>
@@ -4826,31 +4847,34 @@
         <v>12</v>
       </c>
       <c r="B109" t="s">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="C109" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D109" t="s">
         <v>226</v>
       </c>
-      <c r="E109" s="1" t="s">
-        <v>227</v>
+      <c r="E109" s="1">
+        <v>1</v>
       </c>
       <c r="F109" t="s">
-        <v>23</v>
+        <v>62</v>
+      </c>
+      <c r="G109" t="s">
+        <v>17</v>
       </c>
       <c r="I109" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J109" s="2">
         <v>46332.25</v>
       </c>
       <c r="K109" s="2">
-        <v>46336.041666666664</v>
+        <v>46332.75</v>
       </c>
       <c r="L109" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="110" spans="1:12">
@@ -4864,10 +4888,10 @@
         <v>14</v>
       </c>
       <c r="D110" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F110" t="s">
         <v>23</v>
@@ -4890,25 +4914,28 @@
         <v>12</v>
       </c>
       <c r="B111" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="C111" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="D111" t="s">
-        <v>87</v>
+        <v>227</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>228</v>
       </c>
       <c r="F111" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="I111" t="s">
         <v>18</v>
       </c>
       <c r="J111" s="2">
-        <v>46332.291666666664</v>
+        <v>46332.25</v>
       </c>
       <c r="K111" s="2">
-        <v>46332.791666666664</v>
+        <v>46336.041666666664</v>
       </c>
       <c r="L111" t="s">
         <v>43</v>
@@ -4919,27 +4946,56 @@
         <v>12</v>
       </c>
       <c r="B112" t="s">
+        <v>48</v>
+      </c>
+      <c r="C112" t="s">
+        <v>49</v>
+      </c>
+      <c r="D112" t="s">
+        <v>90</v>
+      </c>
+      <c r="F112" t="s">
+        <v>52</v>
+      </c>
+      <c r="I112" t="s">
+        <v>18</v>
+      </c>
+      <c r="J112" s="2">
+        <v>46332.291666666664</v>
+      </c>
+      <c r="K112" s="2">
+        <v>46332.791666666664</v>
+      </c>
+      <c r="L112" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12">
+      <c r="A113" t="s">
+        <v>12</v>
+      </c>
+      <c r="B113" t="s">
         <v>65</v>
       </c>
-      <c r="C112" t="s">
-        <v>97</v>
-      </c>
-      <c r="D112" t="s">
-        <v>98</v>
-      </c>
-      <c r="F112" t="s">
+      <c r="C113" t="s">
+        <v>100</v>
+      </c>
+      <c r="D113" t="s">
+        <v>101</v>
+      </c>
+      <c r="F113" t="s">
         <v>68</v>
       </c>
-      <c r="I112" t="s">
-        <v>18</v>
-      </c>
-      <c r="J112" s="2">
+      <c r="I113" t="s">
+        <v>18</v>
+      </c>
+      <c r="J113" s="2">
         <v>46332.541666666664</v>
       </c>
-      <c r="K112" s="2">
+      <c r="K113" s="2">
         <v>46333.041666666664</v>
       </c>
-      <c r="L112" t="s">
+      <c r="L113" t="s">
         <v>43</v>
       </c>
     </row>
@@ -4952,29 +5008,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<scriptIds xmlns="http://schemas.microsoft.com/office/extensibility/maker/v1.0" id="script-ids-node-id">
-  <scriptId id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFlYmU2eGFOY1prSzQ4ZzMwOVNrOE5z"/>
-  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJYSQ36AWKC2TNDYVMQR2CLHJFKM:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQVNodndMS0ZxYlI0cXlFZENXZEpWTUFiamQ5UnJqRGdfNHFKblptMGRDaTk4"/>
-  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFjcU1YSmx2clY5eXMzT2hWMXFuc2ZZ"/>
-</scriptIds>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
 </p:properties>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A69D21F4021FF043AD25F7555C34E75C" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ada5bbc6177f3d5462a6af737539cf89">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="169fe4b0-aa95-4062-90d3-821d069df163" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ce4529c032f5bb0135a70d700e81f25b" ns2:_="">
     <xsd:import namespace="169fe4b0-aa95-4062-90d3-821d069df163"/>
@@ -5112,18 +5151,35 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<scriptIds xmlns="http://schemas.microsoft.com/office/extensibility/maker/v1.0" id="script-ids-node-id">
+  <scriptId id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFlYmU2eGFOY1prSzQ4ZzMwOVNrOE5z"/>
+  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJYSQ36AWKC2TNDYVMQR2CLHJFKM:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQVNodndMS0ZxYlI0cXlFZENXZEpWTUFiamQ5UnJqRGdfNHFKblptMGRDaTk4"/>
+  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFjcU1YSmx2clY5eXMzT2hWMXFuc2ZZ"/>
+</scriptIds>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF8193A-09E0-4717-9CA6-EF5C70C0F2A4}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D94EB81F-BDF3-4640-AE12-B1EC3B704FEB}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{090E8699-A26C-4C66-9B6D-70C00CB2CACE}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF03C61-A585-446F-A57D-D94F9FA6CAC8}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF8193A-09E0-4717-9CA6-EF5C70C0F2A4}"/>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D94EB81F-BDF3-4640-AE12-B1EC3B704FEB}"/>
 </file>